--- a/copart_lots.xlsx
+++ b/copart_lots.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U337"/>
+  <dimension ref="A1:U338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26267,12 +26267,12 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>93572125</t>
+          <t>93393345</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LE</t>
+          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>XLE PREMIUM</t>
         </is>
       </c>
       <c r="G285" s="4" t="inlineStr">
@@ -26305,34 +26305,46 @@
       </c>
       <c r="I285" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J285" s="3" t="inlineStr"/>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J285" s="3" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
       <c r="K285" s="5" t="n">
-        <v>14195</v>
+        <v>3832</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>29346</v>
+        <v>37270</v>
       </c>
       <c r="M285" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O285" s="3" t="inlineStr">
         <is>
-          <t>NV - LAS VEGAS WEST</t>
-        </is>
-      </c>
-      <c r="P285" s="3" t="inlineStr"/>
-      <c r="Q285" s="3" t="inlineStr"/>
+          <t>MI - DETROIT</t>
+        </is>
+      </c>
+      <c r="P285" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-17 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q285" s="3" t="inlineStr">
+        <is>
+          <t>CLEAN TITLE</t>
+        </is>
+      </c>
       <c r="R285" s="3" t="inlineStr">
         <is>
-          <t>2T3F1RFV5SW******</t>
+          <t>2T3A1RFV5SC******</t>
         </is>
       </c>
       <c r="S285" s="3" t="inlineStr">
@@ -26342,24 +26354,24 @@
       </c>
       <c r="T285" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 12:39:57 UTC</t>
+          <t>2026-03-15 05:45:15 UTC</t>
         </is>
       </c>
       <c r="U285" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/93572125/2025-toyota-rav4-le-nv-las-vegas-west</t>
+          <t>https://www.copart.com/lot/93393345/clean-title-2025-toyota-rav4-xle-premium-mi-detroit</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>93623875</t>
+          <t>93572125</t>
         </is>
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C286" s="6" t="n">
@@ -26377,12 +26389,12 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G286" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="G286" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H286" s="6" t="inlineStr">
@@ -26392,19 +26404,15 @@
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="J286" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J286" s="6" t="inlineStr"/>
       <c r="K286" s="7" t="n">
-        <v>38</v>
+        <v>14195</v>
       </c>
       <c r="L286" s="7" t="n">
-        <v>31860</v>
+        <v>29346</v>
       </c>
       <c r="M286" s="7" t="n">
         <v>0</v>
@@ -26416,22 +26424,14 @@
       </c>
       <c r="O286" s="6" t="inlineStr">
         <is>
-          <t>SC - COLUMBIA</t>
-        </is>
-      </c>
-      <c r="P286" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-13 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q286" s="6" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>NV - LAS VEGAS WEST</t>
+        </is>
+      </c>
+      <c r="P286" s="6" t="inlineStr"/>
+      <c r="Q286" s="6" t="inlineStr"/>
       <c r="R286" s="6" t="inlineStr">
         <is>
-          <t>2T3W1RFV8SC******</t>
+          <t>2T3F1RFV5SW******</t>
         </is>
       </c>
       <c r="S286" s="6" t="inlineStr">
@@ -26446,23 +26446,23 @@
       </c>
       <c r="U286" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/93623875/salvage-2025-toyota-rav4-xle-sc-columbia</t>
+          <t>https://www.copart.com/lot/93572125/2025-toyota-rav4-le-nv-las-vegas-west</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>93749375</t>
+          <t>93623875</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
@@ -26479,9 +26479,9 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="G287" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
@@ -26491,32 +26491,36 @@
       </c>
       <c r="I287" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J287" s="3" t="inlineStr"/>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J287" s="3" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
       <c r="K287" s="5" t="n">
-        <v>18655</v>
+        <v>38</v>
       </c>
       <c r="L287" s="5" t="n">
-        <v>28354</v>
+        <v>31860</v>
       </c>
       <c r="M287" s="5" t="n">
-        <v>2050</v>
+        <v>0</v>
       </c>
       <c r="N287" s="3" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O287" s="3" t="inlineStr">
         <is>
-          <t>HI - HONOLULU</t>
+          <t>SC - COLUMBIA</t>
         </is>
       </c>
       <c r="P287" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16 22:00 UTC</t>
+          <t>2026-03-13 14:00 UTC</t>
         </is>
       </c>
       <c r="Q287" s="3" t="inlineStr">
@@ -26526,7 +26530,7 @@
       </c>
       <c r="R287" s="3" t="inlineStr">
         <is>
-          <t>JTMW1RFV4ND******</t>
+          <t>2T3W1RFV8SC******</t>
         </is>
       </c>
       <c r="S287" s="3" t="inlineStr">
@@ -26541,23 +26545,23 @@
       </c>
       <c r="U287" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/93749375/salvage-2022-toyota-rav4-xle-hi-honolulu</t>
+          <t>https://www.copart.com/lot/93623875/salvage-2025-toyota-rav4-xle-sc-columbia</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>93836135</t>
+          <t>93749375</t>
         </is>
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 LE</t>
+          <t>2022 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C288" s="6" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
@@ -26571,7 +26575,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G288" s="4" t="inlineStr">
@@ -26586,38 +26590,42 @@
       </c>
       <c r="I288" s="6" t="inlineStr">
         <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="J288" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J288" s="6" t="inlineStr"/>
       <c r="K288" s="7" t="n">
-        <v>10810</v>
+        <v>18655</v>
       </c>
       <c r="L288" s="7" t="n">
-        <v>27359</v>
+        <v>28354</v>
       </c>
       <c r="M288" s="7" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="N288" s="6" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O288" s="6" t="inlineStr">
         <is>
-          <t>NC - CHINA GROVE</t>
-        </is>
-      </c>
-      <c r="P288" s="6" t="inlineStr"/>
-      <c r="Q288" s="6" t="inlineStr"/>
+          <t>HI - HONOLULU</t>
+        </is>
+      </c>
+      <c r="P288" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q288" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R288" s="6" t="inlineStr">
         <is>
-          <t>2T3H1RFV5RW******</t>
+          <t>JTMW1RFV4ND******</t>
         </is>
       </c>
       <c r="S288" s="6" t="inlineStr">
@@ -26632,23 +26640,23 @@
       </c>
       <c r="U288" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/93836135/2024-toyota-rav4-le-nc-china-grove</t>
+          <t>https://www.copart.com/lot/93749375/salvage-2022-toyota-rav4-xle-hi-honolulu</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>94063445</t>
+          <t>93836135</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2024 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
@@ -26662,7 +26670,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -26677,22 +26685,22 @@
       </c>
       <c r="I289" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>SIDE</t>
         </is>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
+          <t>FRONT END</t>
         </is>
       </c>
       <c r="K289" s="5" t="n">
-        <v>8292</v>
+        <v>10810</v>
       </c>
       <c r="L289" s="5" t="n">
-        <v>36756</v>
+        <v>27359</v>
       </c>
       <c r="M289" s="5" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
@@ -26701,22 +26709,14 @@
       </c>
       <c r="O289" s="3" t="inlineStr">
         <is>
-          <t>TN - KNOXVILLE</t>
-        </is>
-      </c>
-      <c r="P289" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-17 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q289" s="3" t="inlineStr">
-        <is>
-          <t>CLEAN TITLE</t>
-        </is>
-      </c>
+          <t>NC - CHINA GROVE</t>
+        </is>
+      </c>
+      <c r="P289" s="3" t="inlineStr"/>
+      <c r="Q289" s="3" t="inlineStr"/>
       <c r="R289" s="3" t="inlineStr">
         <is>
-          <t>2T3P1RFV7SW******</t>
+          <t>2T3H1RFV5RW******</t>
         </is>
       </c>
       <c r="S289" s="3" t="inlineStr">
@@ -26731,23 +26731,23 @@
       </c>
       <c r="U289" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/94063445/clean-title-2025-toyota-rav4-xle-tn-knoxville</t>
+          <t>https://www.copart.com/lot/93836135/2024-toyota-rav4-le-nc-china-grove</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>94176365</t>
+          <t>94063445</t>
         </is>
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>2023 TOYOTA RAV4 LE</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C290" s="6" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
@@ -26761,12 +26761,12 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G290" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G290" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H290" s="6" t="inlineStr">
@@ -26776,18 +26776,22 @@
       </c>
       <c r="I290" s="6" t="inlineStr">
         <is>
-          <t>MINOR DENT/SCRATCHES</t>
-        </is>
-      </c>
-      <c r="J290" s="6" t="inlineStr"/>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J290" s="6" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
       <c r="K290" s="7" t="n">
-        <v>14513</v>
+        <v>8292</v>
       </c>
       <c r="L290" s="7" t="n">
-        <v>32281</v>
+        <v>36756</v>
       </c>
       <c r="M290" s="7" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="N290" s="6" t="inlineStr">
         <is>
@@ -26796,14 +26800,22 @@
       </c>
       <c r="O290" s="6" t="inlineStr">
         <is>
-          <t>CO - DENVER CENTRAL</t>
-        </is>
-      </c>
-      <c r="P290" s="6" t="inlineStr"/>
-      <c r="Q290" s="6" t="inlineStr"/>
+          <t>TN - KNOXVILLE</t>
+        </is>
+      </c>
+      <c r="P290" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q290" s="6" t="inlineStr">
+        <is>
+          <t>CLEAN TITLE</t>
+        </is>
+      </c>
       <c r="R290" s="6" t="inlineStr">
         <is>
-          <t>JTMMWRFVXPD******</t>
+          <t>2T3P1RFV7SW******</t>
         </is>
       </c>
       <c r="S290" s="6" t="inlineStr">
@@ -26818,23 +26830,23 @@
       </c>
       <c r="U290" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/94176365/2023-toyota-rav4-le-co-denver-central</t>
+          <t>https://www.copart.com/lot/94063445/clean-title-2025-toyota-rav4-xle-tn-knoxville</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>94223525</t>
+          <t>94176365</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LE</t>
+          <t>2023 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
@@ -26851,9 +26863,9 @@
           <t>LE</t>
         </is>
       </c>
-      <c r="G291" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
@@ -26863,19 +26875,15 @@
       </c>
       <c r="I291" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="J291" s="3" t="inlineStr">
-        <is>
           <t>MINOR DENT/SCRATCHES</t>
         </is>
       </c>
+      <c r="J291" s="3" t="inlineStr"/>
       <c r="K291" s="5" t="n">
-        <v>2520</v>
+        <v>14513</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>32269</v>
+        <v>32281</v>
       </c>
       <c r="M291" s="5" t="n">
         <v>0</v>
@@ -26887,22 +26895,14 @@
       </c>
       <c r="O291" s="3" t="inlineStr">
         <is>
-          <t>MI - FLINT</t>
-        </is>
-      </c>
-      <c r="P291" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-18 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q291" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>CO - DENVER CENTRAL</t>
+        </is>
+      </c>
+      <c r="P291" s="3" t="inlineStr"/>
+      <c r="Q291" s="3" t="inlineStr"/>
       <c r="R291" s="3" t="inlineStr">
         <is>
-          <t>2T3F1RFV5SW******</t>
+          <t>JTMMWRFVXPD******</t>
         </is>
       </c>
       <c r="S291" s="3" t="inlineStr">
@@ -26917,19 +26917,19 @@
       </c>
       <c r="U291" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/94223525/salvage-2025-toyota-rav4-le-mi-flint</t>
+          <t>https://www.copart.com/lot/94176365/2023-toyota-rav4-le-co-denver-central</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>94259325</t>
+          <t>94223525</t>
         </is>
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 HYBRID</t>
+          <t>2025 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C292" s="6" t="n">
@@ -26942,13 +26942,17 @@
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>RAV4 HYBRID</t>
-        </is>
-      </c>
-      <c r="F292" s="6" t="inlineStr"/>
-      <c r="G292" s="6" t="inlineStr">
-        <is>
-          <t>ENGINE START PROGRAM</t>
+          <t>RAV4</t>
+        </is>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H292" s="6" t="inlineStr">
@@ -26963,17 +26967,17 @@
       </c>
       <c r="J292" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>MINOR DENT/SCRATCHES</t>
         </is>
       </c>
       <c r="K292" s="7" t="n">
-        <v>8411</v>
+        <v>2520</v>
       </c>
       <c r="L292" s="7" t="n">
-        <v>35570</v>
+        <v>32269</v>
       </c>
       <c r="M292" s="7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N292" s="6" t="inlineStr">
         <is>
@@ -26982,12 +26986,12 @@
       </c>
       <c r="O292" s="6" t="inlineStr">
         <is>
-          <t>FL - PUNTA GORDA</t>
+          <t>MI - FLINT</t>
         </is>
       </c>
       <c r="P292" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13 14:00 UTC</t>
+          <t>2026-03-18 14:00 UTC</t>
         </is>
       </c>
       <c r="Q292" s="6" t="inlineStr">
@@ -26997,7 +27001,7 @@
       </c>
       <c r="R292" s="6" t="inlineStr">
         <is>
-          <t>2T3RWRFV3SW******</t>
+          <t>2T3F1RFV5SW******</t>
         </is>
       </c>
       <c r="S292" s="6" t="inlineStr">
@@ -27012,23 +27016,23 @@
       </c>
       <c r="U292" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/94259325/salvage-2025-toyota-rav4-hybrid-fl-punta-gorda</t>
+          <t>https://www.copart.com/lot/94223525/salvage-2025-toyota-rav4-le-mi-flint</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>94784805</t>
+          <t>94259325</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 HYBRID</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
@@ -27037,17 +27041,13 @@
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>RAV4</t>
-        </is>
-      </c>
-      <c r="F293" s="3" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G293" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>RAV4 HYBRID</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr"/>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>ENGINE START PROGRAM</t>
         </is>
       </c>
       <c r="H293" s="3" t="inlineStr">
@@ -27057,18 +27057,22 @@
       </c>
       <c r="I293" s="3" t="inlineStr">
         <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J293" s="3" t="inlineStr">
+        <is>
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J293" s="3" t="inlineStr"/>
       <c r="K293" s="5" t="n">
-        <v>28069</v>
+        <v>8411</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>27130</v>
+        <v>35570</v>
       </c>
       <c r="M293" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
@@ -27077,14 +27081,22 @@
       </c>
       <c r="O293" s="3" t="inlineStr">
         <is>
-          <t>NV - LAS VEGAS</t>
-        </is>
-      </c>
-      <c r="P293" s="3" t="inlineStr"/>
-      <c r="Q293" s="3" t="inlineStr"/>
+          <t>FL - PUNTA GORDA</t>
+        </is>
+      </c>
+      <c r="P293" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-13 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q293" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R293" s="3" t="inlineStr">
         <is>
-          <t>2T3W1RFV1NC******</t>
+          <t>2T3RWRFV3SW******</t>
         </is>
       </c>
       <c r="S293" s="3" t="inlineStr">
@@ -27099,23 +27111,23 @@
       </c>
       <c r="U293" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/94784805/2022-toyota-rav4-xle-nv-las-vegas</t>
+          <t>https://www.copart.com/lot/94259325/salvage-2025-toyota-rav4-hybrid-fl-punta-gorda</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>94908045</t>
+          <t>94784805</t>
         </is>
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2022 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C294" s="6" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D294" s="6" t="inlineStr">
         <is>
@@ -27132,9 +27144,9 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="G294" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+      <c r="G294" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H294" s="6" t="inlineStr">
@@ -27147,16 +27159,12 @@
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J294" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+      <c r="J294" s="6" t="inlineStr"/>
       <c r="K294" s="7" t="n">
-        <v>11093</v>
+        <v>28069</v>
       </c>
       <c r="L294" s="7" t="n">
-        <v>-1</v>
+        <v>27130</v>
       </c>
       <c r="M294" s="7" t="n">
         <v>0</v>
@@ -27168,14 +27176,14 @@
       </c>
       <c r="O294" s="6" t="inlineStr">
         <is>
-          <t>NC - CHINA GROVE</t>
+          <t>NV - LAS VEGAS</t>
         </is>
       </c>
       <c r="P294" s="6" t="inlineStr"/>
       <c r="Q294" s="6" t="inlineStr"/>
       <c r="R294" s="6" t="inlineStr">
         <is>
-          <t>2T3RWRFV4SW******</t>
+          <t>2T3W1RFV1NC******</t>
         </is>
       </c>
       <c r="S294" s="6" t="inlineStr">
@@ -27190,19 +27198,19 @@
       </c>
       <c r="U294" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/94908045/2025-toyota-rav4-xle-nc-china-grove</t>
+          <t>https://www.copart.com/lot/94784805/2022-toyota-rav4-xle-nv-las-vegas</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>95162315</t>
+          <t>94908045</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LE</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -27220,12 +27228,12 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G295" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H295" s="3" t="inlineStr">
@@ -27235,19 +27243,19 @@
       </c>
       <c r="I295" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
+          <t>REAR END</t>
         </is>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>FRONT END</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>5102</v>
+        <v>11093</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>33407</v>
+        <v>-1</v>
       </c>
       <c r="M295" s="5" t="n">
         <v>0</v>
@@ -27259,22 +27267,14 @@
       </c>
       <c r="O295" s="3" t="inlineStr">
         <is>
-          <t>CA - ADELANTO</t>
-        </is>
-      </c>
-      <c r="P295" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q295" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>NC - CHINA GROVE</t>
+        </is>
+      </c>
+      <c r="P295" s="3" t="inlineStr"/>
+      <c r="Q295" s="3" t="inlineStr"/>
       <c r="R295" s="3" t="inlineStr">
         <is>
-          <t>JTMMWRFV5SD******</t>
+          <t>2T3RWRFV4SW******</t>
         </is>
       </c>
       <c r="S295" s="3" t="inlineStr">
@@ -27289,19 +27289,19 @@
       </c>
       <c r="U295" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/95162315/salvage-2025-toyota-rav4-le-ca-adelanto</t>
+          <t>https://www.copart.com/lot/94908045/2025-toyota-rav4-xle-nc-china-grove</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>95398775</t>
+          <t>95162315</t>
         </is>
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C296" s="6" t="n">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
@@ -27334,19 +27334,19 @@
       </c>
       <c r="I296" s="6" t="inlineStr">
         <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J296" s="6" t="inlineStr">
+        <is>
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J296" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
       <c r="K296" s="7" t="n">
-        <v>8712</v>
+        <v>5102</v>
       </c>
       <c r="L296" s="7" t="n">
-        <v>30042</v>
+        <v>33407</v>
       </c>
       <c r="M296" s="7" t="n">
         <v>0</v>
@@ -27358,14 +27358,22 @@
       </c>
       <c r="O296" s="6" t="inlineStr">
         <is>
-          <t>FL - TAMPA SOUTH</t>
-        </is>
-      </c>
-      <c r="P296" s="6" t="inlineStr"/>
-      <c r="Q296" s="6" t="inlineStr"/>
+          <t>CA - ADELANTO</t>
+        </is>
+      </c>
+      <c r="P296" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q296" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R296" s="6" t="inlineStr">
         <is>
-          <t>2T3W1RFV7SW******</t>
+          <t>JTMMWRFV5SD******</t>
         </is>
       </c>
       <c r="S296" s="6" t="inlineStr">
@@ -27380,19 +27388,19 @@
       </c>
       <c r="U296" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/95398775/2025-toyota-rav4-xle-fl-tampa-south</t>
+          <t>https://www.copart.com/lot/95162315/salvage-2025-toyota-rav4-le-ca-adelanto</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>95513485</t>
+          <t>95398775</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 WOODLAND EDITION</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -27410,17 +27418,17 @@
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>WOODLAND EDITION</t>
-        </is>
-      </c>
-      <c r="G297" s="3" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G297" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H297" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I297" s="3" t="inlineStr">
@@ -27434,10 +27442,10 @@
         </is>
       </c>
       <c r="K297" s="5" t="n">
-        <v>16399</v>
+        <v>8712</v>
       </c>
       <c r="L297" s="5" t="n">
-        <v>35755</v>
+        <v>30042</v>
       </c>
       <c r="M297" s="5" t="n">
         <v>0</v>
@@ -27449,18 +27457,14 @@
       </c>
       <c r="O297" s="3" t="inlineStr">
         <is>
-          <t>CO - DENVER SOUTH</t>
+          <t>FL - TAMPA SOUTH</t>
         </is>
       </c>
       <c r="P297" s="3" t="inlineStr"/>
-      <c r="Q297" s="3" t="inlineStr">
-        <is>
-          <t>CLEAN TITLE</t>
-        </is>
-      </c>
+      <c r="Q297" s="3" t="inlineStr"/>
       <c r="R297" s="3" t="inlineStr">
         <is>
-          <t>2T3UWRFV1SW******</t>
+          <t>2T3W1RFV7SW******</t>
         </is>
       </c>
       <c r="S297" s="3" t="inlineStr">
@@ -27475,23 +27479,23 @@
       </c>
       <c r="U297" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/95513485/clean-title-2025-toyota-rav4-woodland-edition-co-denver-south</t>
+          <t>https://www.copart.com/lot/95398775/2025-toyota-rav4-xle-fl-tampa-south</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>95953315</t>
+          <t>95513485</t>
         </is>
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XSE</t>
+          <t>2025 TOYOTA RAV4 WOODLAND EDITION</t>
         </is>
       </c>
       <c r="C298" s="6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D298" s="6" t="inlineStr">
         <is>
@@ -27505,17 +27509,17 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>XSE</t>
-        </is>
-      </c>
-      <c r="G298" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>WOODLAND EDITION</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I298" s="6" t="inlineStr">
@@ -27523,12 +27527,16 @@
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J298" s="6" t="inlineStr"/>
+      <c r="J298" s="6" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
       <c r="K298" s="7" t="n">
-        <v>14736</v>
+        <v>16399</v>
       </c>
       <c r="L298" s="7" t="n">
-        <v>35220</v>
+        <v>35755</v>
       </c>
       <c r="M298" s="7" t="n">
         <v>0</v>
@@ -27540,14 +27548,18 @@
       </c>
       <c r="O298" s="6" t="inlineStr">
         <is>
-          <t>OH - DAYTON</t>
+          <t>CO - DENVER SOUTH</t>
         </is>
       </c>
       <c r="P298" s="6" t="inlineStr"/>
-      <c r="Q298" s="6" t="inlineStr"/>
+      <c r="Q298" s="6" t="inlineStr">
+        <is>
+          <t>CLEAN TITLE</t>
+        </is>
+      </c>
       <c r="R298" s="6" t="inlineStr">
         <is>
-          <t>JTME6RFV2RD******</t>
+          <t>2T3UWRFV1SW******</t>
         </is>
       </c>
       <c r="S298" s="6" t="inlineStr">
@@ -27562,23 +27574,23 @@
       </c>
       <c r="U298" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/95953315/2024-toyota-rav4-xse-oh-dayton</t>
+          <t>https://www.copart.com/lot/95513485/clean-title-2025-toyota-rav4-woodland-edition-co-denver-south</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>96336575</t>
+          <t>95953315</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>2023 TOYOTA RAV4 XLE</t>
+          <t>2024 TOYOTA RAV4 XSE</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
@@ -27592,32 +27604,30 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G299" s="3" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>XSE</t>
+        </is>
+      </c>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H299" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I299" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="J299" s="3" t="inlineStr">
-        <is>
-          <t>MINOR DENT/SCRATCHES</t>
-        </is>
-      </c>
-      <c r="K299" s="5" t="inlineStr"/>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J299" s="3" t="inlineStr"/>
+      <c r="K299" s="5" t="n">
+        <v>14736</v>
+      </c>
       <c r="L299" s="5" t="n">
-        <v>24537</v>
+        <v>35220</v>
       </c>
       <c r="M299" s="5" t="n">
         <v>0</v>
@@ -27629,22 +27639,14 @@
       </c>
       <c r="O299" s="3" t="inlineStr">
         <is>
-          <t>MD - BALTIMORE</t>
-        </is>
-      </c>
-      <c r="P299" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-16 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q299" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>OH - DAYTON</t>
+        </is>
+      </c>
+      <c r="P299" s="3" t="inlineStr"/>
+      <c r="Q299" s="3" t="inlineStr"/>
       <c r="R299" s="3" t="inlineStr">
         <is>
-          <t>2T3P1RFV4PC******</t>
+          <t>JTME6RFV2RD******</t>
         </is>
       </c>
       <c r="S299" s="3" t="inlineStr">
@@ -27659,23 +27661,23 @@
       </c>
       <c r="U299" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/96336575/salvage-2023-toyota-rav4-xle-md-baltimore</t>
+          <t>https://www.copart.com/lot/95953315/2024-toyota-rav4-xse-oh-dayton</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>96349765</t>
+          <t>96336575</t>
         </is>
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024 TOYOTA RAV4 HYBRID   </t>
+          <t>2023 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C300" s="6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D300" s="6" t="inlineStr">
         <is>
@@ -27684,7 +27686,7 @@
       </c>
       <c r="E300" s="6" t="inlineStr">
         <is>
-          <t>RAV4 HYBRID</t>
+          <t>RAV4</t>
         </is>
       </c>
       <c r="F300" s="6" t="inlineStr">
@@ -27699,7 +27701,7 @@
       </c>
       <c r="H300" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I300" s="6" t="inlineStr">
@@ -27712,11 +27714,9 @@
           <t>MINOR DENT/SCRATCHES</t>
         </is>
       </c>
-      <c r="K300" s="7" t="n">
-        <v>16810</v>
-      </c>
+      <c r="K300" s="7" t="inlineStr"/>
       <c r="L300" s="7" t="n">
-        <v>31913</v>
+        <v>24537</v>
       </c>
       <c r="M300" s="7" t="n">
         <v>0</v>
@@ -27728,10 +27728,14 @@
       </c>
       <c r="O300" s="6" t="inlineStr">
         <is>
-          <t>MD - LAUREL</t>
-        </is>
-      </c>
-      <c r="P300" s="6" t="inlineStr"/>
+          <t>MD - BALTIMORE</t>
+        </is>
+      </c>
+      <c r="P300" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16 14:00 UTC</t>
+        </is>
+      </c>
       <c r="Q300" s="6" t="inlineStr">
         <is>
           <t>SALVAGE TITLE</t>
@@ -27739,7 +27743,7 @@
       </c>
       <c r="R300" s="6" t="inlineStr">
         <is>
-          <t>JTMRWRFV3RD******</t>
+          <t>2T3P1RFV4PC******</t>
         </is>
       </c>
       <c r="S300" s="6" t="inlineStr">
@@ -27754,23 +27758,23 @@
       </c>
       <c r="U300" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/96349765/salvage-2024-toyota-rav4-hybrid-md-laurel</t>
+          <t>https://www.copart.com/lot/96336575/salvage-2023-toyota-rav4-xle-md-baltimore</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>96478455</t>
+          <t>96349765</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t xml:space="preserve">2024 TOYOTA RAV4 HYBRID   </t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
@@ -27779,7 +27783,7 @@
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>RAV4</t>
+          <t>RAV4 HYBRID</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -27787,9 +27791,9 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="G301" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H301" s="3" t="inlineStr">
@@ -27802,12 +27806,16 @@
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J301" s="3" t="inlineStr"/>
+      <c r="J301" s="3" t="inlineStr">
+        <is>
+          <t>MINOR DENT/SCRATCHES</t>
+        </is>
+      </c>
       <c r="K301" s="5" t="n">
-        <v>12345</v>
+        <v>16810</v>
       </c>
       <c r="L301" s="5" t="n">
-        <v>43023</v>
+        <v>31913</v>
       </c>
       <c r="M301" s="5" t="n">
         <v>0</v>
@@ -27819,14 +27827,18 @@
       </c>
       <c r="O301" s="3" t="inlineStr">
         <is>
-          <t>ON - LONDON</t>
+          <t>MD - LAUREL</t>
         </is>
       </c>
       <c r="P301" s="3" t="inlineStr"/>
-      <c r="Q301" s="3" t="inlineStr"/>
+      <c r="Q301" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R301" s="3" t="inlineStr">
         <is>
-          <t>2T3R1RFV6SC******</t>
+          <t>JTMRWRFV3RD******</t>
         </is>
       </c>
       <c r="S301" s="3" t="inlineStr">
@@ -27841,23 +27853,23 @@
       </c>
       <c r="U301" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/96478455/2025-toyota-rav4-xle-on-london</t>
+          <t>https://www.copart.com/lot/96349765/salvage-2024-toyota-rav4-hybrid-md-laurel</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>96703915</t>
+          <t>96478455</t>
         </is>
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C302" s="6" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D302" s="6" t="inlineStr">
         <is>
@@ -27871,12 +27883,12 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
-        </is>
-      </c>
-      <c r="G302" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H302" s="6" t="inlineStr">
@@ -27889,14 +27901,12 @@
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J302" s="6" t="inlineStr">
-        <is>
-          <t>ALL OVER</t>
-        </is>
-      </c>
-      <c r="K302" s="7" t="inlineStr"/>
+      <c r="J302" s="6" t="inlineStr"/>
+      <c r="K302" s="7" t="n">
+        <v>12345</v>
+      </c>
       <c r="L302" s="7" t="n">
-        <v>25970</v>
+        <v>43023</v>
       </c>
       <c r="M302" s="7" t="n">
         <v>0</v>
@@ -27908,18 +27918,14 @@
       </c>
       <c r="O302" s="6" t="inlineStr">
         <is>
-          <t>NC - LUMBERTON</t>
+          <t>ON - LONDON</t>
         </is>
       </c>
       <c r="P302" s="6" t="inlineStr"/>
-      <c r="Q302" s="6" t="inlineStr">
-        <is>
-          <t>CLEAN TITLE</t>
-        </is>
-      </c>
+      <c r="Q302" s="6" t="inlineStr"/>
       <c r="R302" s="6" t="inlineStr">
         <is>
-          <t>2T3C1RFV8NW******</t>
+          <t>2T3R1RFV6SC******</t>
         </is>
       </c>
       <c r="S302" s="6" t="inlineStr">
@@ -27934,23 +27940,23 @@
       </c>
       <c r="U302" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/96703915/clean-title-2022-toyota-rav4-xle-premium-nc-lumberton</t>
+          <t>https://www.copart.com/lot/96478455/2025-toyota-rav4-xle-on-london</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>97021765</t>
+          <t>96703915</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>2023 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
@@ -27979,42 +27985,40 @@
       </c>
       <c r="I303" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J303" s="3" t="inlineStr"/>
-      <c r="K303" s="5" t="n">
-        <v>25603</v>
-      </c>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J303" s="3" t="inlineStr">
+        <is>
+          <t>ALL OVER</t>
+        </is>
+      </c>
+      <c r="K303" s="5" t="inlineStr"/>
       <c r="L303" s="5" t="n">
-        <v>36808</v>
+        <v>25970</v>
       </c>
       <c r="M303" s="5" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="N303" s="3" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O303" s="3" t="inlineStr">
         <is>
-          <t>OR - EUGENE</t>
-        </is>
-      </c>
-      <c r="P303" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-31 19:00 UTC</t>
-        </is>
-      </c>
+          <t>NC - LUMBERTON</t>
+        </is>
+      </c>
+      <c r="P303" s="3" t="inlineStr"/>
       <c r="Q303" s="3" t="inlineStr">
         <is>
-          <t>SALVAGE TITLE</t>
+          <t>CLEAN TITLE</t>
         </is>
       </c>
       <c r="R303" s="3" t="inlineStr">
         <is>
-          <t>JTMB6RFV8PD******</t>
+          <t>2T3C1RFV8NW******</t>
         </is>
       </c>
       <c r="S303" s="3" t="inlineStr">
@@ -28029,23 +28033,23 @@
       </c>
       <c r="U303" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97021765/salvage-2023-toyota-rav4-xle-premium-or-eugene</t>
+          <t>https://www.copart.com/lot/96703915/clean-title-2022-toyota-rav4-xle-premium-nc-lumberton</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>97200235</t>
+          <t>97021765</t>
         </is>
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2023 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C304" s="6" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D304" s="6" t="inlineStr">
         <is>
@@ -28059,12 +28063,12 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G304" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G304" s="6" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H304" s="6" t="inlineStr">
@@ -28079,29 +28083,37 @@
       </c>
       <c r="J304" s="6" t="inlineStr"/>
       <c r="K304" s="7" t="n">
-        <v>6959</v>
+        <v>25603</v>
       </c>
       <c r="L304" s="7" t="n">
-        <v>36357</v>
+        <v>36808</v>
       </c>
       <c r="M304" s="7" t="n">
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="N304" s="6" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O304" s="6" t="inlineStr">
         <is>
-          <t>PA - PHILADELPHIA</t>
-        </is>
-      </c>
-      <c r="P304" s="6" t="inlineStr"/>
-      <c r="Q304" s="6" t="inlineStr"/>
+          <t>OR - EUGENE</t>
+        </is>
+      </c>
+      <c r="P304" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q304" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R304" s="6" t="inlineStr">
         <is>
-          <t>2T3RWRFV7SW******</t>
+          <t>JTMB6RFV8PD******</t>
         </is>
       </c>
       <c r="S304" s="6" t="inlineStr">
@@ -28116,14 +28128,14 @@
       </c>
       <c r="U304" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97200235/2025-toyota-rav4-xle-pa-philadelphia</t>
+          <t>https://www.copart.com/lot/97021765/salvage-2023-toyota-rav4-xle-premium-or-eugene</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>97224615</t>
+          <t>97200235</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
@@ -28166,10 +28178,10 @@
       </c>
       <c r="J305" s="3" t="inlineStr"/>
       <c r="K305" s="5" t="n">
-        <v>1414</v>
+        <v>6959</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>41575</v>
+        <v>36357</v>
       </c>
       <c r="M305" s="5" t="n">
         <v>0</v>
@@ -28181,14 +28193,14 @@
       </c>
       <c r="O305" s="3" t="inlineStr">
         <is>
-          <t>CO - DENVER</t>
+          <t>PA - PHILADELPHIA</t>
         </is>
       </c>
       <c r="P305" s="3" t="inlineStr"/>
       <c r="Q305" s="3" t="inlineStr"/>
       <c r="R305" s="3" t="inlineStr">
         <is>
-          <t>JTMRWRFV3SD******</t>
+          <t>2T3RWRFV7SW******</t>
         </is>
       </c>
       <c r="S305" s="3" t="inlineStr">
@@ -28203,23 +28215,23 @@
       </c>
       <c r="U305" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97224615/2025-toyota-rav4-xle-co-denver</t>
+          <t>https://www.copart.com/lot/97200235/2025-toyota-rav4-xle-pa-philadelphia</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>97456575</t>
+          <t>97224615</t>
         </is>
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C306" s="6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D306" s="6" t="inlineStr">
         <is>
@@ -28253,10 +28265,10 @@
       </c>
       <c r="J306" s="6" t="inlineStr"/>
       <c r="K306" s="7" t="n">
-        <v>28266</v>
+        <v>1414</v>
       </c>
       <c r="L306" s="7" t="n">
-        <v>28675</v>
+        <v>41575</v>
       </c>
       <c r="M306" s="7" t="n">
         <v>0</v>
@@ -28268,14 +28280,14 @@
       </c>
       <c r="O306" s="6" t="inlineStr">
         <is>
-          <t>FL - CLEWISTON</t>
+          <t>CO - DENVER</t>
         </is>
       </c>
       <c r="P306" s="6" t="inlineStr"/>
       <c r="Q306" s="6" t="inlineStr"/>
       <c r="R306" s="6" t="inlineStr">
         <is>
-          <t>2T3W1RFV8RC******</t>
+          <t>JTMRWRFV3SD******</t>
         </is>
       </c>
       <c r="S306" s="6" t="inlineStr">
@@ -28290,23 +28302,23 @@
       </c>
       <c r="U306" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97456575/2024-toyota-rav4-xle-fl-clewiston</t>
+          <t>https://www.copart.com/lot/97224615/2025-toyota-rav4-xle-co-denver</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>97522025</t>
+          <t>97456575</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D307" s="3" t="inlineStr">
         <is>
@@ -28320,7 +28332,7 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -28335,42 +28347,34 @@
       </c>
       <c r="I307" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
+          <t>REAR END</t>
         </is>
       </c>
       <c r="J307" s="3" t="inlineStr"/>
       <c r="K307" s="5" t="n">
-        <v>22762</v>
+        <v>28266</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>28034</v>
+        <v>28675</v>
       </c>
       <c r="M307" s="5" t="n">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="N307" s="3" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O307" s="3" t="inlineStr">
         <is>
-          <t>OH - CLEVELAND EAST</t>
-        </is>
-      </c>
-      <c r="P307" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-11 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q307" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>FL - CLEWISTON</t>
+        </is>
+      </c>
+      <c r="P307" s="3" t="inlineStr"/>
+      <c r="Q307" s="3" t="inlineStr"/>
       <c r="R307" s="3" t="inlineStr">
         <is>
-          <t>2T3F1RFV4SW******</t>
+          <t>2T3W1RFV8RC******</t>
         </is>
       </c>
       <c r="S307" s="3" t="inlineStr">
@@ -28385,19 +28389,19 @@
       </c>
       <c r="U307" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97522025/salvage-2025-toyota-rav4-le-oh-cleveland-east</t>
+          <t>https://www.copart.com/lot/97456575/2024-toyota-rav4-xle-fl-clewiston</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>97631295</t>
+          <t>97522025</t>
         </is>
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C308" s="6" t="n">
@@ -28415,7 +28419,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G308" s="4" t="inlineStr">
@@ -28430,34 +28434,42 @@
       </c>
       <c r="I308" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>SIDE</t>
         </is>
       </c>
       <c r="J308" s="6" t="inlineStr"/>
       <c r="K308" s="7" t="n">
-        <v>928</v>
+        <v>22762</v>
       </c>
       <c r="L308" s="7" t="n">
-        <v>30528</v>
+        <v>28034</v>
       </c>
       <c r="M308" s="7" t="n">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="N308" s="6" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O308" s="6" t="inlineStr">
         <is>
-          <t>FL - MIAMI CENTRAL</t>
-        </is>
-      </c>
-      <c r="P308" s="6" t="inlineStr"/>
-      <c r="Q308" s="6" t="inlineStr"/>
+          <t>OH - CLEVELAND EAST</t>
+        </is>
+      </c>
+      <c r="P308" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-11 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q308" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R308" s="6" t="inlineStr">
         <is>
-          <t>2T3W1RFVXSC******</t>
+          <t>2T3F1RFV4SW******</t>
         </is>
       </c>
       <c r="S308" s="6" t="inlineStr">
@@ -28472,19 +28484,19 @@
       </c>
       <c r="U308" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97631295/2025-toyota-rav4-xle-fl-miami-central</t>
+          <t>https://www.copart.com/lot/97522025/salvage-2025-toyota-rav4-le-oh-cleveland-east</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>97679635</t>
+          <t>97631295</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025 TOYOTA RAV4   </t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -28502,7 +28514,7 @@
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
-          <t>XSE</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G309" s="4" t="inlineStr">
@@ -28517,19 +28529,15 @@
       </c>
       <c r="I309" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="J309" s="3" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J309" s="3" t="inlineStr"/>
       <c r="K309" s="5" t="n">
-        <v>3133</v>
+        <v>928</v>
       </c>
       <c r="L309" s="5" t="n">
-        <v>46424</v>
+        <v>30528</v>
       </c>
       <c r="M309" s="5" t="n">
         <v>0</v>
@@ -28541,22 +28549,14 @@
       </c>
       <c r="O309" s="3" t="inlineStr">
         <is>
-          <t>CA - SUN VALLEY</t>
-        </is>
-      </c>
-      <c r="P309" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q309" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>FL - MIAMI CENTRAL</t>
+        </is>
+      </c>
+      <c r="P309" s="3" t="inlineStr"/>
+      <c r="Q309" s="3" t="inlineStr"/>
       <c r="R309" s="3" t="inlineStr">
         <is>
-          <t>JTMEB3FV2SD******</t>
+          <t>2T3W1RFVXSC******</t>
         </is>
       </c>
       <c r="S309" s="3" t="inlineStr">
@@ -28571,23 +28571,23 @@
       </c>
       <c r="U309" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97679635/salvage-2025-toyota-rav4-ca-sun-valley</t>
+          <t>https://www.copart.com/lot/97631295/2025-toyota-rav4-xle-fl-miami-central</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>97744195</t>
+          <t>97679635</t>
         </is>
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 PRIME XSE</t>
+          <t xml:space="preserve">2025 TOYOTA RAV4   </t>
         </is>
       </c>
       <c r="C310" s="6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D310" s="6" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
       </c>
       <c r="E310" s="6" t="inlineStr">
         <is>
-          <t>RAV4 PRIME</t>
+          <t>RAV4</t>
         </is>
       </c>
       <c r="F310" s="6" t="inlineStr">
@@ -28604,14 +28604,14 @@
           <t>XSE</t>
         </is>
       </c>
-      <c r="G310" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+      <c r="G310" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H310" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I310" s="6" t="inlineStr">
@@ -28625,10 +28625,10 @@
         </is>
       </c>
       <c r="K310" s="7" t="n">
-        <v>11454</v>
+        <v>3133</v>
       </c>
       <c r="L310" s="7" t="n">
-        <v>47500</v>
+        <v>46424</v>
       </c>
       <c r="M310" s="7" t="n">
         <v>0</v>
@@ -28640,14 +28640,22 @@
       </c>
       <c r="O310" s="6" t="inlineStr">
         <is>
-          <t>CO - DENVER</t>
-        </is>
-      </c>
-      <c r="P310" s="6" t="inlineStr"/>
-      <c r="Q310" s="6" t="inlineStr"/>
+          <t>CA - SUN VALLEY</t>
+        </is>
+      </c>
+      <c r="P310" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q310" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R310" s="6" t="inlineStr">
         <is>
-          <t>JTMFB3FV2RD******</t>
+          <t>JTMEB3FV2SD******</t>
         </is>
       </c>
       <c r="S310" s="6" t="inlineStr">
@@ -28662,23 +28670,23 @@
       </c>
       <c r="U310" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97744195/2024-toyota-rav4-prime-xse-co-denver</t>
+          <t>https://www.copart.com/lot/97679635/salvage-2025-toyota-rav4-ca-sun-valley</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>97759175</t>
+          <t>97744195</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>2023 TOYOTA RAV4 PRIME XSE</t>
+          <t>2024 TOYOTA RAV4 PRIME XSE</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
@@ -28702,7 +28710,7 @@
       </c>
       <c r="H311" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I311" s="3" t="inlineStr">
@@ -28710,10 +28718,16 @@
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J311" s="3" t="inlineStr"/>
-      <c r="K311" s="5" t="inlineStr"/>
+      <c r="J311" s="3" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
+      <c r="K311" s="5" t="n">
+        <v>11454</v>
+      </c>
       <c r="L311" s="5" t="n">
-        <v>46405</v>
+        <v>47500</v>
       </c>
       <c r="M311" s="5" t="n">
         <v>0</v>
@@ -28725,22 +28739,14 @@
       </c>
       <c r="O311" s="3" t="inlineStr">
         <is>
-          <t>QC - MONTREAL</t>
-        </is>
-      </c>
-      <c r="P311" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-17 16:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q311" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>CO - DENVER</t>
+        </is>
+      </c>
+      <c r="P311" s="3" t="inlineStr"/>
+      <c r="Q311" s="3" t="inlineStr"/>
       <c r="R311" s="3" t="inlineStr">
         <is>
-          <t>JTMGB3FV2PD******</t>
+          <t>JTMFB3FV2RD******</t>
         </is>
       </c>
       <c r="S311" s="3" t="inlineStr">
@@ -28755,23 +28761,23 @@
       </c>
       <c r="U311" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97759175/salvage-2023-toyota-rav4-prime-xse-qc-montreal</t>
+          <t>https://www.copart.com/lot/97744195/2024-toyota-rav4-prime-xse-co-denver</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>97760065</t>
+          <t>97759175</t>
         </is>
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE</t>
+          <t>2023 TOYOTA RAV4 PRIME XSE</t>
         </is>
       </c>
       <c r="C312" s="6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D312" s="6" t="inlineStr">
         <is>
@@ -28780,12 +28786,12 @@
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>RAV4</t>
+          <t>RAV4 PRIME</t>
         </is>
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XSE</t>
         </is>
       </c>
       <c r="G312" s="6" t="inlineStr">
@@ -28800,15 +28806,13 @@
       </c>
       <c r="I312" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>SIDE</t>
         </is>
       </c>
       <c r="J312" s="6" t="inlineStr"/>
-      <c r="K312" s="7" t="n">
-        <v>23563</v>
-      </c>
+      <c r="K312" s="7" t="inlineStr"/>
       <c r="L312" s="7" t="n">
-        <v>-1</v>
+        <v>46405</v>
       </c>
       <c r="M312" s="7" t="n">
         <v>0</v>
@@ -28820,14 +28824,22 @@
       </c>
       <c r="O312" s="6" t="inlineStr">
         <is>
-          <t>MA - FREETOWN</t>
-        </is>
-      </c>
-      <c r="P312" s="6" t="inlineStr"/>
-      <c r="Q312" s="6" t="inlineStr"/>
+          <t>QC - MONTREAL</t>
+        </is>
+      </c>
+      <c r="P312" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q312" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R312" s="6" t="inlineStr">
         <is>
-          <t>JTMRWRFV7RD******</t>
+          <t>JTMGB3FV2PD******</t>
         </is>
       </c>
       <c r="S312" s="6" t="inlineStr">
@@ -28842,23 +28854,23 @@
       </c>
       <c r="U312" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97760065/2024-toyota-rav4-xle-ma-freetown</t>
+          <t>https://www.copart.com/lot/97759175/salvage-2023-toyota-rav4-prime-xse-qc-montreal</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>97765795</t>
+          <t>97760065</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2024 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D313" s="3" t="inlineStr">
         <is>
@@ -28872,12 +28884,12 @@
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
-        </is>
-      </c>
-      <c r="G313" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H313" s="3" t="inlineStr">
@@ -28887,46 +28899,34 @@
       </c>
       <c r="I313" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="J313" s="3" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J313" s="3" t="inlineStr"/>
       <c r="K313" s="5" t="n">
-        <v>5282</v>
+        <v>23563</v>
       </c>
       <c r="L313" s="5" t="n">
-        <v>40656</v>
+        <v>-1</v>
       </c>
       <c r="M313" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N313" s="3" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O313" s="3" t="inlineStr">
         <is>
-          <t>TX - HOUSTON</t>
-        </is>
-      </c>
-      <c r="P313" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-13 17:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q313" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>MA - FREETOWN</t>
+        </is>
+      </c>
+      <c r="P313" s="3" t="inlineStr"/>
+      <c r="Q313" s="3" t="inlineStr"/>
       <c r="R313" s="3" t="inlineStr">
         <is>
-          <t>2T3C1RFV4SC******</t>
+          <t>JTMRWRFV7RD******</t>
         </is>
       </c>
       <c r="S313" s="3" t="inlineStr">
@@ -28941,23 +28941,23 @@
       </c>
       <c r="U313" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97765795/salvage-2025-toyota-rav4-xle-premium-tx-houston</t>
+          <t>https://www.copart.com/lot/97760065/2024-toyota-rav4-xle-ma-freetown</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>97935105</t>
+          <t>97765795</t>
         </is>
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 LE</t>
+          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C314" s="6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D314" s="6" t="inlineStr">
         <is>
@@ -28971,12 +28971,12 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G314" s="6" t="inlineStr">
-        <is>
-          <t>ENGINE START PROGRAM</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G314" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H314" s="6" t="inlineStr">
@@ -28995,29 +28995,37 @@
         </is>
       </c>
       <c r="K314" s="7" t="n">
-        <v>21624</v>
+        <v>5282</v>
       </c>
       <c r="L314" s="7" t="n">
-        <v>-1</v>
+        <v>40656</v>
       </c>
       <c r="M314" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N314" s="6" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O314" s="6" t="inlineStr">
         <is>
-          <t>AZ - PHOENIX NORTH</t>
-        </is>
-      </c>
-      <c r="P314" s="6" t="inlineStr"/>
-      <c r="Q314" s="6" t="inlineStr"/>
+          <t>TX - HOUSTON</t>
+        </is>
+      </c>
+      <c r="P314" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-13 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q314" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R314" s="6" t="inlineStr">
         <is>
-          <t>2T3LWRFV0RW******</t>
+          <t>2T3C1RFV4SC******</t>
         </is>
       </c>
       <c r="S314" s="6" t="inlineStr">
@@ -29032,23 +29040,23 @@
       </c>
       <c r="U314" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97935105/2024-toyota-rav4-le-az-phoenix-north</t>
+          <t>https://www.copart.com/lot/97765795/salvage-2025-toyota-rav4-xle-premium-tx-houston</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>97936265</t>
+          <t>97935105</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2024 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
@@ -29062,12 +29070,12 @@
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>ENGINE START PROGRAM</t>
         </is>
       </c>
       <c r="H315" s="3" t="inlineStr">
@@ -29077,15 +29085,19 @@
       </c>
       <c r="I315" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J315" s="3" t="inlineStr"/>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J315" s="3" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
       <c r="K315" s="5" t="n">
-        <v>4643</v>
+        <v>21624</v>
       </c>
       <c r="L315" s="5" t="n">
-        <v>39555</v>
+        <v>-1</v>
       </c>
       <c r="M315" s="5" t="n">
         <v>0</v>
@@ -29097,18 +29109,14 @@
       </c>
       <c r="O315" s="3" t="inlineStr">
         <is>
-          <t>IL - CHICAGO NORTH</t>
+          <t>AZ - PHOENIX NORTH</t>
         </is>
       </c>
       <c r="P315" s="3" t="inlineStr"/>
-      <c r="Q315" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+      <c r="Q315" s="3" t="inlineStr"/>
       <c r="R315" s="3" t="inlineStr">
         <is>
-          <t>4T3B6RFV0SU******</t>
+          <t>2T3LWRFV0RW******</t>
         </is>
       </c>
       <c r="S315" s="3" t="inlineStr">
@@ -29123,19 +29131,19 @@
       </c>
       <c r="U315" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/97936265/salvage-2025-toyota-rav4-xle-premium-il-chicago-north</t>
+          <t>https://www.copart.com/lot/97935105/2024-toyota-rav4-le-az-phoenix-north</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>98249005</t>
+          <t>97936265</t>
         </is>
       </c>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C316" s="6" t="n">
@@ -29153,12 +29161,12 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G316" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G316" s="6" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H316" s="6" t="inlineStr">
@@ -29171,16 +29179,12 @@
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J316" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+      <c r="J316" s="6" t="inlineStr"/>
       <c r="K316" s="7" t="n">
-        <v>6791</v>
+        <v>4643</v>
       </c>
       <c r="L316" s="7" t="n">
-        <v>-1</v>
+        <v>39555</v>
       </c>
       <c r="M316" s="7" t="n">
         <v>0</v>
@@ -29192,14 +29196,18 @@
       </c>
       <c r="O316" s="6" t="inlineStr">
         <is>
-          <t>FL - ORLANDO NORTH</t>
+          <t>IL - CHICAGO NORTH</t>
         </is>
       </c>
       <c r="P316" s="6" t="inlineStr"/>
-      <c r="Q316" s="6" t="inlineStr"/>
+      <c r="Q316" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R316" s="6" t="inlineStr">
         <is>
-          <t>2T3W1RFV5SC******</t>
+          <t>4T3B6RFV0SU******</t>
         </is>
       </c>
       <c r="S316" s="6" t="inlineStr">
@@ -29214,23 +29222,23 @@
       </c>
       <c r="U316" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98249005/2025-toyota-rav4-xle-fl-orlando-north</t>
+          <t>https://www.copart.com/lot/97936265/salvage-2025-toyota-rav4-xle-premium-il-chicago-north</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>98285395</t>
+          <t>98249005</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
@@ -29259,19 +29267,19 @@
       </c>
       <c r="I317" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
+          <t>REAR END</t>
         </is>
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>UNDERCARRIAGE</t>
+          <t>FRONT END</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>12183</v>
+        <v>6791</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>31233</v>
+        <v>-1</v>
       </c>
       <c r="M317" s="5" t="n">
         <v>0</v>
@@ -29283,27 +29291,19 @@
       </c>
       <c r="O317" s="3" t="inlineStr">
         <is>
-          <t>CA - FRESNO</t>
-        </is>
-      </c>
-      <c r="P317" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q317" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>FL - ORLANDO NORTH</t>
+        </is>
+      </c>
+      <c r="P317" s="3" t="inlineStr"/>
+      <c r="Q317" s="3" t="inlineStr"/>
       <c r="R317" s="3" t="inlineStr">
         <is>
-          <t>2T3W1RFV9RW******</t>
+          <t>2T3W1RFV5SC******</t>
         </is>
       </c>
       <c r="S317" s="3" t="inlineStr">
         <is>
-          <t>2.5L 4</t>
+          <t>2.5L  4</t>
         </is>
       </c>
       <c r="T317" s="3" t="inlineStr">
@@ -29313,19 +29313,19 @@
       </c>
       <c r="U317" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98285395/salvage-2024-toyota-rav4-xle-ca-fresno</t>
+          <t>https://www.copart.com/lot/98249005/2025-toyota-rav4-xle-fl-orlando-north</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>98336845</t>
+          <t>98285395</t>
         </is>
       </c>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C318" s="6" t="n">
@@ -29343,10 +29343,14 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G318" s="6" t="inlineStr"/>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G318" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
+        </is>
+      </c>
       <c r="H318" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -29359,14 +29363,14 @@
       </c>
       <c r="J318" s="6" t="inlineStr">
         <is>
-          <t>FRONT END</t>
+          <t>UNDERCARRIAGE</t>
         </is>
       </c>
       <c r="K318" s="7" t="n">
-        <v>23714</v>
+        <v>12183</v>
       </c>
       <c r="L318" s="7" t="n">
-        <v>31247</v>
+        <v>31233</v>
       </c>
       <c r="M318" s="7" t="n">
         <v>0</v>
@@ -29378,19 +29382,27 @@
       </c>
       <c r="O318" s="6" t="inlineStr">
         <is>
-          <t>CA - SO SACRAMENTO</t>
-        </is>
-      </c>
-      <c r="P318" s="6" t="inlineStr"/>
-      <c r="Q318" s="6" t="inlineStr"/>
+          <t>CA - FRESNO</t>
+        </is>
+      </c>
+      <c r="P318" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q318" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R318" s="6" t="inlineStr">
         <is>
-          <t>4T3LWRFV8RU******</t>
+          <t>2T3W1RFV9RW******</t>
         </is>
       </c>
       <c r="S318" s="6" t="inlineStr">
         <is>
-          <t>2.5L  4</t>
+          <t>2.5L 4</t>
         </is>
       </c>
       <c r="T318" s="6" t="inlineStr">
@@ -29400,19 +29412,19 @@
       </c>
       <c r="U318" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98336845/2024-toyota-rav4-le-ca-so-sacramento</t>
+          <t>https://www.copart.com/lot/98285395/salvage-2024-toyota-rav4-xle-ca-fresno</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>98433755</t>
+          <t>98336845</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE</t>
+          <t>2024 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -29430,14 +29442,10 @@
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G319" s="3" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
-        </is>
-      </c>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr"/>
       <c r="H319" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -29448,10 +29456,16 @@
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J319" s="3" t="inlineStr"/>
-      <c r="K319" s="5" t="inlineStr"/>
+      <c r="J319" s="3" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
+      <c r="K319" s="5" t="n">
+        <v>23714</v>
+      </c>
       <c r="L319" s="5" t="n">
-        <v>30650</v>
+        <v>31247</v>
       </c>
       <c r="M319" s="5" t="n">
         <v>0</v>
@@ -29463,22 +29477,14 @@
       </c>
       <c r="O319" s="3" t="inlineStr">
         <is>
-          <t>IN - DYER</t>
-        </is>
-      </c>
-      <c r="P319" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-06 17:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q319" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>CA - SO SACRAMENTO</t>
+        </is>
+      </c>
+      <c r="P319" s="3" t="inlineStr"/>
+      <c r="Q319" s="3" t="inlineStr"/>
       <c r="R319" s="3" t="inlineStr">
         <is>
-          <t>2T3P1RFVXRC******</t>
+          <t>4T3LWRFV8RU******</t>
         </is>
       </c>
       <c r="S319" s="3" t="inlineStr">
@@ -29493,23 +29499,23 @@
       </c>
       <c r="U319" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98433755/salvage-2024-toyota-rav4-xle-in-dyer</t>
+          <t>https://www.copart.com/lot/98336845/2024-toyota-rav4-le-ca-so-sacramento</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>98542125</t>
+          <t>98433755</t>
         </is>
       </c>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2024 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C320" s="6" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
@@ -29523,7 +29529,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G320" s="6" t="inlineStr">
@@ -29533,7 +29539,7 @@
       </c>
       <c r="H320" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I320" s="6" t="inlineStr">
@@ -29541,16 +29547,10 @@
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J320" s="6" t="inlineStr">
-        <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="K320" s="7" t="n">
-        <v>21333</v>
-      </c>
+      <c r="J320" s="6" t="inlineStr"/>
+      <c r="K320" s="7" t="inlineStr"/>
       <c r="L320" s="7" t="n">
-        <v>-1</v>
+        <v>30650</v>
       </c>
       <c r="M320" s="7" t="n">
         <v>0</v>
@@ -29562,14 +29562,22 @@
       </c>
       <c r="O320" s="6" t="inlineStr">
         <is>
-          <t>NC - CONCORD</t>
-        </is>
-      </c>
-      <c r="P320" s="6" t="inlineStr"/>
-      <c r="Q320" s="6" t="inlineStr"/>
+          <t>IN - DYER</t>
+        </is>
+      </c>
+      <c r="P320" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-06 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q320" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R320" s="6" t="inlineStr">
         <is>
-          <t>2T3C1RFV6NC******</t>
+          <t>2T3P1RFVXRC******</t>
         </is>
       </c>
       <c r="S320" s="6" t="inlineStr">
@@ -29584,23 +29592,23 @@
       </c>
       <c r="U320" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98542125/2022-toyota-rav4-xle-premium-nc-concord</t>
+          <t>https://www.copart.com/lot/98433755/salvage-2024-toyota-rav4-xle-in-dyer</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>98621805</t>
+          <t>98542125</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 LE</t>
+          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
@@ -29614,34 +29622,34 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G321" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H321" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I321" s="3" t="inlineStr">
         <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J321" s="3" t="inlineStr">
+        <is>
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J321" s="3" t="inlineStr">
-        <is>
-          <t>SIDE</t>
-        </is>
-      </c>
       <c r="K321" s="5" t="n">
-        <v>7098</v>
+        <v>21333</v>
       </c>
       <c r="L321" s="5" t="n">
-        <v>31022</v>
+        <v>-1</v>
       </c>
       <c r="M321" s="5" t="n">
         <v>0</v>
@@ -29653,14 +29661,14 @@
       </c>
       <c r="O321" s="3" t="inlineStr">
         <is>
-          <t>TN - NASHVILLE</t>
+          <t>NC - CONCORD</t>
         </is>
       </c>
       <c r="P321" s="3" t="inlineStr"/>
       <c r="Q321" s="3" t="inlineStr"/>
       <c r="R321" s="3" t="inlineStr">
         <is>
-          <t>2T3F1RFVXRW******</t>
+          <t>2T3C1RFV6NC******</t>
         </is>
       </c>
       <c r="S321" s="3" t="inlineStr">
@@ -29675,23 +29683,23 @@
       </c>
       <c r="U321" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98621805/2024-toyota-rav4-le-tn-nashville</t>
+          <t>https://www.copart.com/lot/98542125/2022-toyota-rav4-xle-premium-nc-concord</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>98678215</t>
+          <t>98621805</t>
         </is>
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>2023 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C322" s="6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D322" s="6" t="inlineStr">
         <is>
@@ -29720,15 +29728,19 @@
       </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J322" s="6" t="inlineStr">
+        <is>
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J322" s="6" t="inlineStr"/>
       <c r="K322" s="7" t="n">
-        <v>21857</v>
+        <v>7098</v>
       </c>
       <c r="L322" s="7" t="n">
-        <v>28236</v>
+        <v>31022</v>
       </c>
       <c r="M322" s="7" t="n">
         <v>0</v>
@@ -29740,22 +29752,14 @@
       </c>
       <c r="O322" s="6" t="inlineStr">
         <is>
-          <t>MA - FREETOWN</t>
-        </is>
-      </c>
-      <c r="P322" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-25 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q322" s="6" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>TN - NASHVILLE</t>
+        </is>
+      </c>
+      <c r="P322" s="6" t="inlineStr"/>
+      <c r="Q322" s="6" t="inlineStr"/>
       <c r="R322" s="6" t="inlineStr">
         <is>
-          <t>2T3F1RFV5PC******</t>
+          <t>2T3F1RFVXRW******</t>
         </is>
       </c>
       <c r="S322" s="6" t="inlineStr">
@@ -29770,23 +29774,23 @@
       </c>
       <c r="U322" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98678215/salvage-2023-toyota-rav4-le-ma-freetown</t>
+          <t>https://www.copart.com/lot/98621805/2024-toyota-rav4-le-tn-nashville</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>98937535</t>
+          <t>98678215</t>
         </is>
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LIMITED</t>
+          <t>2023 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
@@ -29800,7 +29804,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>LIMITED</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G323" s="4" t="inlineStr">
@@ -29815,15 +29819,15 @@
       </c>
       <c r="I323" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>SIDE</t>
         </is>
       </c>
       <c r="J323" s="3" t="inlineStr"/>
       <c r="K323" s="5" t="n">
-        <v>2393</v>
+        <v>21857</v>
       </c>
       <c r="L323" s="5" t="n">
-        <v>38492</v>
+        <v>28236</v>
       </c>
       <c r="M323" s="5" t="n">
         <v>0</v>
@@ -29835,14 +29839,22 @@
       </c>
       <c r="O323" s="3" t="inlineStr">
         <is>
-          <t>MN - MINNEAPOLIS NORTH</t>
-        </is>
-      </c>
-      <c r="P323" s="3" t="inlineStr"/>
-      <c r="Q323" s="3" t="inlineStr"/>
+          <t>MA - FREETOWN</t>
+        </is>
+      </c>
+      <c r="P323" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-25 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q323" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R323" s="3" t="inlineStr">
         <is>
-          <t>2T3N1RFV2SW******</t>
+          <t>2T3F1RFV5PC******</t>
         </is>
       </c>
       <c r="S323" s="3" t="inlineStr">
@@ -29857,19 +29869,19 @@
       </c>
       <c r="U323" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98937535/2025-toyota-rav4-limited-mn-minneapolis-north</t>
+          <t>https://www.copart.com/lot/98678215/salvage-2023-toyota-rav4-le-ma-freetown</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>99205765</t>
+          <t>98937535</t>
         </is>
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4</t>
+          <t>2025 TOYOTA RAV4 LIMITED</t>
         </is>
       </c>
       <c r="C324" s="6" t="n">
@@ -29885,10 +29897,14 @@
           <t>RAV4</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr"/>
-      <c r="G324" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>LIMITED</t>
+        </is>
+      </c>
+      <c r="G324" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H324" s="6" t="inlineStr">
@@ -29901,16 +29917,12 @@
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J324" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+      <c r="J324" s="6" t="inlineStr"/>
       <c r="K324" s="7" t="n">
-        <v>10449</v>
+        <v>2393</v>
       </c>
       <c r="L324" s="7" t="n">
-        <v>33160</v>
+        <v>38492</v>
       </c>
       <c r="M324" s="7" t="n">
         <v>0</v>
@@ -29922,14 +29934,14 @@
       </c>
       <c r="O324" s="6" t="inlineStr">
         <is>
-          <t>NC - RALEIGH</t>
+          <t>MN - MINNEAPOLIS NORTH</t>
         </is>
       </c>
       <c r="P324" s="6" t="inlineStr"/>
       <c r="Q324" s="6" t="inlineStr"/>
       <c r="R324" s="6" t="inlineStr">
         <is>
-          <t>JTMMWRFV0SD******</t>
+          <t>2T3N1RFV2SW******</t>
         </is>
       </c>
       <c r="S324" s="6" t="inlineStr">
@@ -29944,23 +29956,23 @@
       </c>
       <c r="U324" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99205765/2025-toyota-rav4-nc-raleigh</t>
+          <t>https://www.copart.com/lot/98937535/2025-toyota-rav4-limited-mn-minneapolis-north</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>99216065</t>
+          <t>99205765</t>
         </is>
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 LE</t>
+          <t>2025 TOYOTA RAV4</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
@@ -29972,11 +29984,7 @@
           <t>RAV4</t>
         </is>
       </c>
-      <c r="F325" s="3" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="F325" s="3" t="inlineStr"/>
       <c r="G325" s="3" t="inlineStr">
         <is>
           <t>ENHANCED VEHICLES</t>
@@ -29984,18 +29992,24 @@
       </c>
       <c r="H325" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I325" s="3" t="inlineStr">
         <is>
-          <t>MINOR DENT/SCRATCHES</t>
-        </is>
-      </c>
-      <c r="J325" s="3" t="inlineStr"/>
-      <c r="K325" s="5" t="inlineStr"/>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J325" s="3" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
+      <c r="K325" s="5" t="n">
+        <v>10449</v>
+      </c>
       <c r="L325" s="5" t="n">
-        <v>23908</v>
+        <v>33160</v>
       </c>
       <c r="M325" s="5" t="n">
         <v>0</v>
@@ -30007,18 +30021,14 @@
       </c>
       <c r="O325" s="3" t="inlineStr">
         <is>
-          <t>IL - CHICAGO NORTH</t>
+          <t>NC - RALEIGH</t>
         </is>
       </c>
       <c r="P325" s="3" t="inlineStr"/>
-      <c r="Q325" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+      <c r="Q325" s="3" t="inlineStr"/>
       <c r="R325" s="3" t="inlineStr">
         <is>
-          <t>2T3G1RFV7NW******</t>
+          <t>JTMMWRFV0SD******</t>
         </is>
       </c>
       <c r="S325" s="3" t="inlineStr">
@@ -30033,23 +30043,23 @@
       </c>
       <c r="U325" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99216065/salvage-2022-toyota-rav4-le-il-chicago-north</t>
+          <t>https://www.copart.com/lot/99205765/2025-toyota-rav4-nc-raleigh</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>99251225</t>
+          <t>99216065</t>
         </is>
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 WOODLAND EDITION</t>
+          <t>2022 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C326" s="6" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D326" s="6" t="inlineStr">
         <is>
@@ -30063,7 +30073,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>WOODLAND EDITION</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G326" s="6" t="inlineStr">
@@ -30073,43 +30083,33 @@
       </c>
       <c r="H326" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J326" s="6" t="inlineStr">
-        <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="K326" s="7" t="n">
-        <v>12582</v>
-      </c>
+          <t>MINOR DENT/SCRATCHES</t>
+        </is>
+      </c>
+      <c r="J326" s="6" t="inlineStr"/>
+      <c r="K326" s="7" t="inlineStr"/>
       <c r="L326" s="7" t="n">
-        <v>35294</v>
+        <v>23908</v>
       </c>
       <c r="M326" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N326" s="6" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O326" s="6" t="inlineStr">
         <is>
-          <t>CO - DENVER</t>
-        </is>
-      </c>
-      <c r="P326" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-24 18:00 UTC</t>
-        </is>
-      </c>
+          <t>IL - CHICAGO NORTH</t>
+        </is>
+      </c>
+      <c r="P326" s="6" t="inlineStr"/>
       <c r="Q326" s="6" t="inlineStr">
         <is>
           <t>SALVAGE TITLE</t>
@@ -30117,7 +30117,7 @@
       </c>
       <c r="R326" s="6" t="inlineStr">
         <is>
-          <t>2T3UWRFV3RW******</t>
+          <t>2T3G1RFV7NW******</t>
         </is>
       </c>
       <c r="S326" s="6" t="inlineStr">
@@ -30132,19 +30132,19 @@
       </c>
       <c r="U326" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99251225/salvage-2024-toyota-rav4-woodland-edition-co-denver</t>
+          <t>https://www.copart.com/lot/99216065/salvage-2022-toyota-rav4-le-il-chicago-north</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>99282985</t>
+          <t>99251225</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2024 TOYOTA RAV4 WOODLAND EDITION</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -30162,12 +30162,12 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
-        </is>
-      </c>
-      <c r="G327" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>WOODLAND EDITION</t>
+        </is>
+      </c>
+      <c r="G327" s="3" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H327" s="3" t="inlineStr">
@@ -30177,38 +30177,46 @@
       </c>
       <c r="I327" s="3" t="inlineStr">
         <is>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J327" s="3" t="inlineStr">
+        <is>
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J327" s="3" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
       <c r="K327" s="5" t="n">
-        <v>12493</v>
+        <v>12582</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>33959</v>
+        <v>35294</v>
       </c>
       <c r="M327" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N327" s="3" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O327" s="3" t="inlineStr">
         <is>
-          <t>HI - HONOLULU</t>
-        </is>
-      </c>
-      <c r="P327" s="3" t="inlineStr"/>
-      <c r="Q327" s="3" t="inlineStr"/>
+          <t>CO - DENVER</t>
+        </is>
+      </c>
+      <c r="P327" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-24 18:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q327" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R327" s="3" t="inlineStr">
         <is>
-          <t>JTMC1RFV8RD******</t>
+          <t>2T3UWRFV3RW******</t>
         </is>
       </c>
       <c r="S327" s="3" t="inlineStr">
@@ -30223,23 +30231,23 @@
       </c>
       <c r="U327" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99282985/2024-toyota-rav4-xle-premium-hi-honolulu</t>
+          <t>https://www.copart.com/lot/99251225/salvage-2024-toyota-rav4-woodland-edition-co-denver</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>99392955</t>
+          <t>99282985</t>
         </is>
       </c>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C328" s="6" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
@@ -30253,12 +30261,12 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G328" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G328" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H328" s="6" t="inlineStr">
@@ -30268,15 +30276,19 @@
       </c>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J328" s="6" t="inlineStr"/>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J328" s="6" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
       <c r="K328" s="7" t="n">
-        <v>11244</v>
+        <v>12493</v>
       </c>
       <c r="L328" s="7" t="n">
-        <v>31881</v>
+        <v>33959</v>
       </c>
       <c r="M328" s="7" t="n">
         <v>0</v>
@@ -30288,22 +30300,14 @@
       </c>
       <c r="O328" s="6" t="inlineStr">
         <is>
-          <t>CA - SUN VALLEY</t>
-        </is>
-      </c>
-      <c r="P328" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q328" s="6" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>HI - HONOLULU</t>
+        </is>
+      </c>
+      <c r="P328" s="6" t="inlineStr"/>
+      <c r="Q328" s="6" t="inlineStr"/>
       <c r="R328" s="6" t="inlineStr">
         <is>
-          <t>JTMMWRFV6SD******</t>
+          <t>JTMC1RFV8RD******</t>
         </is>
       </c>
       <c r="S328" s="6" t="inlineStr">
@@ -30318,23 +30322,23 @@
       </c>
       <c r="U328" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99392955/salvage-2025-toyota-rav4-le-ca-sun-valley</t>
+          <t>https://www.copart.com/lot/99282985/2024-toyota-rav4-xle-premium-hi-honolulu</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>99469625</t>
+          <t>99392955</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2025 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
@@ -30348,12 +30352,12 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
-        </is>
-      </c>
-      <c r="G329" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="G329" s="3" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H329" s="3" t="inlineStr">
@@ -30368,27 +30372,27 @@
       </c>
       <c r="J329" s="3" t="inlineStr"/>
       <c r="K329" s="5" t="n">
-        <v>23566</v>
+        <v>11244</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>30084</v>
+        <v>31881</v>
       </c>
       <c r="M329" s="5" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="N329" s="3" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O329" s="3" t="inlineStr">
         <is>
-          <t>TX - DALLAS</t>
+          <t>CA - SUN VALLEY</t>
         </is>
       </c>
       <c r="P329" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12 17:00 UTC</t>
+          <t>2026-03-16 19:00 UTC</t>
         </is>
       </c>
       <c r="Q329" s="3" t="inlineStr">
@@ -30398,7 +30402,7 @@
       </c>
       <c r="R329" s="3" t="inlineStr">
         <is>
-          <t>2T3C1RFV5NW******</t>
+          <t>JTMMWRFV6SD******</t>
         </is>
       </c>
       <c r="S329" s="3" t="inlineStr">
@@ -30413,23 +30417,23 @@
       </c>
       <c r="U329" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99469625/salvage-2022-toyota-rav4-xle-premium-tx-dallas</t>
+          <t>https://www.copart.com/lot/99392955/salvage-2025-toyota-rav4-le-ca-sun-valley</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>99642525</t>
+          <t>99469625</t>
         </is>
       </c>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C330" s="6" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
@@ -30443,12 +30447,12 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G330" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H330" s="6" t="inlineStr">
@@ -30458,38 +30462,42 @@
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="J330" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J330" s="6" t="inlineStr"/>
       <c r="K330" s="7" t="n">
-        <v>14551</v>
+        <v>23566</v>
       </c>
       <c r="L330" s="7" t="n">
-        <v>30815</v>
+        <v>30084</v>
       </c>
       <c r="M330" s="7" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="N330" s="6" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O330" s="6" t="inlineStr">
         <is>
-          <t>VA - RICHMOND</t>
-        </is>
-      </c>
-      <c r="P330" s="6" t="inlineStr"/>
-      <c r="Q330" s="6" t="inlineStr"/>
+          <t>TX - DALLAS</t>
+        </is>
+      </c>
+      <c r="P330" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-12 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q330" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R330" s="6" t="inlineStr">
         <is>
-          <t>JTMRWRFV1SJ******</t>
+          <t>2T3C1RFV5NW******</t>
         </is>
       </c>
       <c r="S330" s="6" t="inlineStr">
@@ -30504,14 +30512,14 @@
       </c>
       <c r="U330" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99642525/2025-toyota-rav4-xle-va-richmond</t>
+          <t>https://www.copart.com/lot/99469625/salvage-2022-toyota-rav4-xle-premium-tx-dallas</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>99770855</t>
+          <t>99642525</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
@@ -30539,7 +30547,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>ENGINE START PROGRAM</t>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H331" s="3" t="inlineStr">
@@ -30554,17 +30562,17 @@
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>FRONT END</t>
         </is>
       </c>
       <c r="K331" s="5" t="n">
-        <v>9078</v>
+        <v>14551</v>
       </c>
       <c r="L331" s="5" t="n">
-        <v>28342</v>
+        <v>30815</v>
       </c>
       <c r="M331" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N331" s="3" t="inlineStr">
         <is>
@@ -30573,27 +30581,19 @@
       </c>
       <c r="O331" s="3" t="inlineStr">
         <is>
-          <t>FL - JACKSONVILLE NORTH</t>
-        </is>
-      </c>
-      <c r="P331" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-11 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q331" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>VA - RICHMOND</t>
+        </is>
+      </c>
+      <c r="P331" s="3" t="inlineStr"/>
+      <c r="Q331" s="3" t="inlineStr"/>
       <c r="R331" s="3" t="inlineStr">
         <is>
-          <t>2T3W1RFV2SC******</t>
+          <t>JTMRWRFV1SJ******</t>
         </is>
       </c>
       <c r="S331" s="3" t="inlineStr">
         <is>
-          <t>2.5L 4</t>
+          <t>2.5L  4</t>
         </is>
       </c>
       <c r="T331" s="3" t="inlineStr">
@@ -30603,19 +30603,19 @@
       </c>
       <c r="U331" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99770855/salvage-2025-toyota-rav4-xle-fl-jacksonville-north</t>
+          <t>https://www.copart.com/lot/99642525/2025-toyota-rav4-xle-va-richmond</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>99780885</t>
+          <t>99770855</t>
         </is>
       </c>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LIMITED</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C332" s="6" t="n">
@@ -30633,7 +30633,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>LIMITED</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G332" s="6" t="inlineStr">
@@ -30653,31 +30653,31 @@
       </c>
       <c r="J332" s="6" t="inlineStr">
         <is>
-          <t>UNDERCARRIAGE</t>
+          <t>REAR END</t>
         </is>
       </c>
       <c r="K332" s="7" t="n">
-        <v>8183</v>
+        <v>9078</v>
       </c>
       <c r="L332" s="7" t="n">
-        <v>-1</v>
+        <v>28342</v>
       </c>
       <c r="M332" s="7" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="N332" s="6" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O332" s="6" t="inlineStr">
         <is>
-          <t>IA - DES MOINES</t>
+          <t>FL - JACKSONVILLE NORTH</t>
         </is>
       </c>
       <c r="P332" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10 17:00 UTC</t>
+          <t>2026-03-11 14:00 UTC</t>
         </is>
       </c>
       <c r="Q332" s="6" t="inlineStr">
@@ -30687,12 +30687,12 @@
       </c>
       <c r="R332" s="6" t="inlineStr">
         <is>
-          <t>4T3D6RFV0SU******</t>
+          <t>2T3W1RFV2SC******</t>
         </is>
       </c>
       <c r="S332" s="6" t="inlineStr">
         <is>
-          <t>2.5L  4</t>
+          <t>2.5L 4</t>
         </is>
       </c>
       <c r="T332" s="6" t="inlineStr">
@@ -30702,19 +30702,19 @@
       </c>
       <c r="U332" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99780885/salvage-2025-toyota-rav4-limited-ia-des-moines</t>
+          <t>https://www.copart.com/lot/99770855/salvage-2025-toyota-rav4-xle-fl-jacksonville-north</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>99781835</t>
+          <t>99780885</t>
         </is>
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 LIMITED</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -30732,12 +30732,12 @@
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G333" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>LIMITED</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>ENGINE START PROGRAM</t>
         </is>
       </c>
       <c r="H333" s="3" t="inlineStr">
@@ -30747,34 +30747,46 @@
       </c>
       <c r="I333" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J333" s="3" t="inlineStr"/>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J333" s="3" t="inlineStr">
+        <is>
+          <t>UNDERCARRIAGE</t>
+        </is>
+      </c>
       <c r="K333" s="5" t="n">
-        <v>11137</v>
+        <v>8183</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>28475</v>
+        <v>-1</v>
       </c>
       <c r="M333" s="5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="N333" s="3" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O333" s="3" t="inlineStr">
         <is>
-          <t>GA - CARTERSVILLE</t>
-        </is>
-      </c>
-      <c r="P333" s="3" t="inlineStr"/>
-      <c r="Q333" s="3" t="inlineStr"/>
+          <t>IA - DES MOINES</t>
+        </is>
+      </c>
+      <c r="P333" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q333" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R333" s="3" t="inlineStr">
         <is>
-          <t>2T3W1RFV2SC******</t>
+          <t>4T3D6RFV0SU******</t>
         </is>
       </c>
       <c r="S333" s="3" t="inlineStr">
@@ -30789,23 +30801,23 @@
       </c>
       <c r="U333" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99781835/2025-toyota-rav4-xle-ga-cartersville</t>
+          <t>https://www.copart.com/lot/99780885/salvage-2025-toyota-rav4-limited-ia-des-moines</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>99813365</t>
+          <t>99781835</t>
         </is>
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C334" s="6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D334" s="6" t="inlineStr">
         <is>
@@ -30834,19 +30846,15 @@
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>VANDALISM</t>
-        </is>
-      </c>
-      <c r="J334" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J334" s="6" t="inlineStr"/>
       <c r="K334" s="7" t="n">
-        <v>28237</v>
+        <v>11137</v>
       </c>
       <c r="L334" s="7" t="n">
-        <v>-1</v>
+        <v>28475</v>
       </c>
       <c r="M334" s="7" t="n">
         <v>0</v>
@@ -30858,14 +30866,14 @@
       </c>
       <c r="O334" s="6" t="inlineStr">
         <is>
-          <t>QC - MONTREAL</t>
+          <t>GA - CARTERSVILLE</t>
         </is>
       </c>
       <c r="P334" s="6" t="inlineStr"/>
       <c r="Q334" s="6" t="inlineStr"/>
       <c r="R334" s="6" t="inlineStr">
         <is>
-          <t>2T3R1RFV5RW******</t>
+          <t>2T3W1RFV2SC******</t>
         </is>
       </c>
       <c r="S334" s="6" t="inlineStr">
@@ -30880,23 +30888,23 @@
       </c>
       <c r="U334" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99813365/2024-toyota-rav4-xle-qc-montreal</t>
+          <t>https://www.copart.com/lot/99781835/2025-toyota-rav4-xle-ga-cartersville</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>99835885</t>
+          <t>99813365</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
@@ -30910,7 +30918,7 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G335" s="4" t="inlineStr">
@@ -30925,46 +30933,38 @@
       </c>
       <c r="I335" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
+          <t>VANDALISM</t>
         </is>
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>FRONT END</t>
         </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>4342</v>
+        <v>28237</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>29066</v>
+        <v>-1</v>
       </c>
       <c r="M335" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N335" s="3" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O335" s="3" t="inlineStr">
         <is>
-          <t>MS - JACKSON</t>
-        </is>
-      </c>
-      <c r="P335" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-13 17:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q335" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>QC - MONTREAL</t>
+        </is>
+      </c>
+      <c r="P335" s="3" t="inlineStr"/>
+      <c r="Q335" s="3" t="inlineStr"/>
       <c r="R335" s="3" t="inlineStr">
         <is>
-          <t>2T3H1RFVXSC******</t>
+          <t>2T3R1RFV5RW******</t>
         </is>
       </c>
       <c r="S335" s="3" t="inlineStr">
@@ -30979,23 +30979,23 @@
       </c>
       <c r="U335" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99835885/salvage-2025-toyota-rav4-le-ms-jackson</t>
+          <t>https://www.copart.com/lot/99813365/2024-toyota-rav4-xle-qc-montreal</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>99850375</t>
+          <t>99835885</t>
         </is>
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>2023 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C336" s="6" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D336" s="6" t="inlineStr">
         <is>
@@ -31009,12 +31009,12 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G336" s="6" t="inlineStr">
-        <is>
-          <t>ENGINE START PROGRAM</t>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H336" s="6" t="inlineStr">
@@ -31024,76 +31024,175 @@
       </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J336" s="6" t="inlineStr">
+        <is>
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J336" s="6" t="inlineStr"/>
       <c r="K336" s="7" t="n">
-        <v>25382</v>
+        <v>4342</v>
       </c>
       <c r="L336" s="7" t="n">
-        <v>29177</v>
+        <v>29066</v>
       </c>
       <c r="M336" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N336" s="6" t="inlineStr">
         <is>
+          <t>✅ NLR</t>
+        </is>
+      </c>
+      <c r="O336" s="6" t="inlineStr">
+        <is>
+          <t>MS - JACKSON</t>
+        </is>
+      </c>
+      <c r="P336" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-13 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q336" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
+      <c r="R336" s="6" t="inlineStr">
+        <is>
+          <t>2T3H1RFVXSC******</t>
+        </is>
+      </c>
+      <c r="S336" s="6" t="inlineStr">
+        <is>
+          <t>2.5L  4</t>
+        </is>
+      </c>
+      <c r="T336" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:39:57 UTC</t>
+        </is>
+      </c>
+      <c r="U336" s="6" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/99835885/salvage-2025-toyota-rav4-le-ms-jackson</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>99850375</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>TOYOTA</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>RAV4</t>
+        </is>
+      </c>
+      <c r="F337" s="3" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr">
+        <is>
+          <t>ENGINE START PROGRAM</t>
+        </is>
+      </c>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I337" s="3" t="inlineStr">
+        <is>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J337" s="3" t="inlineStr"/>
+      <c r="K337" s="5" t="n">
+        <v>25382</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>29177</v>
+      </c>
+      <c r="M337" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N337" s="3" t="inlineStr">
+        <is>
           <t>🔑 Broker</t>
         </is>
       </c>
-      <c r="O336" s="6" t="inlineStr">
+      <c r="O337" s="3" t="inlineStr">
         <is>
           <t>MA - NORTH BOSTON</t>
         </is>
       </c>
-      <c r="P336" s="6" t="inlineStr"/>
-      <c r="Q336" s="6" t="inlineStr"/>
-      <c r="R336" s="6" t="inlineStr">
+      <c r="P337" s="3" t="inlineStr"/>
+      <c r="Q337" s="3" t="inlineStr"/>
+      <c r="R337" s="3" t="inlineStr">
         <is>
           <t>2T3P1RFVXPW******</t>
         </is>
       </c>
-      <c r="S336" s="6" t="inlineStr">
+      <c r="S337" s="3" t="inlineStr">
         <is>
           <t>2.5L  4</t>
         </is>
       </c>
-      <c r="T336" s="6" t="inlineStr">
+      <c r="T337" s="3" t="inlineStr">
         <is>
           <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
-      <c r="U336" s="6" t="inlineStr">
+      <c r="U337" s="3" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/99850375/2023-toyota-rav4-xle-ma-north-boston</t>
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" s="8" t="inlineStr">
+    <row r="338">
+      <c r="A338" s="8" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B337" s="9" t="inlineStr">
-        <is>
-          <t>Total Lots: 334</t>
-        </is>
-      </c>
-      <c r="C337" s="10" t="inlineStr">
-        <is>
-          <t>NLR: 34</t>
-        </is>
-      </c>
-      <c r="D337" s="9" t="inlineStr">
+      <c r="B338" s="9" t="inlineStr">
+        <is>
+          <t>Total Lots: 335</t>
+        </is>
+      </c>
+      <c r="C338" s="10" t="inlineStr">
+        <is>
+          <t>NLR: 35</t>
+        </is>
+      </c>
+      <c r="D338" s="9" t="inlineStr">
         <is>
           <t>Broker: 300</t>
         </is>
       </c>
-      <c r="E337" s="10" t="inlineStr">
-        <is>
-          <t>Runs &amp; Drives: 215</t>
+      <c r="E338" s="10" t="inlineStr">
+        <is>
+          <t>Runs &amp; Drives: 216</t>
         </is>
       </c>
     </row>

--- a/copart_lots.xlsx
+++ b/copart_lots.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U374"/>
+  <dimension ref="A1:U375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32439,16 +32439,16 @@
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>98249005</t>
+          <t>97991205</t>
         </is>
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2024 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -32477,16 +32477,12 @@
       </c>
       <c r="I353" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J353" s="3" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>NORMAL WEAR</t>
+        </is>
+      </c>
+      <c r="J353" s="3" t="inlineStr"/>
       <c r="K353" s="5" t="n">
-        <v>6791</v>
+        <v>17469</v>
       </c>
       <c r="L353" s="5" t="n">
         <v>-1</v>
@@ -32501,14 +32497,22 @@
       </c>
       <c r="O353" s="3" t="inlineStr">
         <is>
-          <t>FL - ORLANDO NORTH</t>
-        </is>
-      </c>
-      <c r="P353" s="3" t="inlineStr"/>
-      <c r="Q353" s="3" t="inlineStr"/>
+          <t>FL - MIAMI SOUTH</t>
+        </is>
+      </c>
+      <c r="P353" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-24 16:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q353" s="3" t="inlineStr">
+        <is>
+          <t>CLEAN TITLE</t>
+        </is>
+      </c>
       <c r="R353" s="3" t="inlineStr">
         <is>
-          <t>2T3W1RFV5SC******</t>
+          <t>2T3H1RFV8RC******</t>
         </is>
       </c>
       <c r="S353" s="3" t="inlineStr">
@@ -32518,28 +32522,28 @@
       </c>
       <c r="T353" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11 12:39:57 UTC</t>
+          <t>2026-03-19 14:39:59 UTC</t>
         </is>
       </c>
       <c r="U353" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98249005/2025-toyota-rav4-xle-fl-orlando-north</t>
+          <t>https://www.copart.com/lot/97991205/clean-title-2024-toyota-rav4-le-fl-miami-south</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>98285395</t>
+          <t>98249005</t>
         </is>
       </c>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C354" s="6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
@@ -32568,19 +32572,19 @@
       </c>
       <c r="I354" s="6" t="inlineStr">
         <is>
-          <t>SIDE</t>
+          <t>REAR END</t>
         </is>
       </c>
       <c r="J354" s="6" t="inlineStr">
         <is>
-          <t>UNDERCARRIAGE</t>
+          <t>FRONT END</t>
         </is>
       </c>
       <c r="K354" s="7" t="n">
-        <v>12183</v>
+        <v>6791</v>
       </c>
       <c r="L354" s="7" t="n">
-        <v>31233</v>
+        <v>-1</v>
       </c>
       <c r="M354" s="7" t="n">
         <v>0</v>
@@ -32592,27 +32596,19 @@
       </c>
       <c r="O354" s="6" t="inlineStr">
         <is>
-          <t>CA - FRESNO</t>
-        </is>
-      </c>
-      <c r="P354" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q354" s="6" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>FL - ORLANDO NORTH</t>
+        </is>
+      </c>
+      <c r="P354" s="6" t="inlineStr"/>
+      <c r="Q354" s="6" t="inlineStr"/>
       <c r="R354" s="6" t="inlineStr">
         <is>
-          <t>2T3W1RFV9RW******</t>
+          <t>2T3W1RFV5SC******</t>
         </is>
       </c>
       <c r="S354" s="6" t="inlineStr">
         <is>
-          <t>2.5L 4</t>
+          <t>2.5L  4</t>
         </is>
       </c>
       <c r="T354" s="6" t="inlineStr">
@@ -32622,19 +32618,19 @@
       </c>
       <c r="U354" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98285395/salvage-2024-toyota-rav4-xle-ca-fresno</t>
+          <t>https://www.copart.com/lot/98249005/2025-toyota-rav4-xle-fl-orlando-north</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>98336845</t>
+          <t>98285395</t>
         </is>
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -32652,10 +32648,14 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G355" s="3" t="inlineStr"/>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G355" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
+        </is>
+      </c>
       <c r="H355" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -32668,14 +32668,14 @@
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
-          <t>FRONT END</t>
+          <t>UNDERCARRIAGE</t>
         </is>
       </c>
       <c r="K355" s="5" t="n">
-        <v>23714</v>
+        <v>12183</v>
       </c>
       <c r="L355" s="5" t="n">
-        <v>31247</v>
+        <v>31233</v>
       </c>
       <c r="M355" s="5" t="n">
         <v>0</v>
@@ -32687,19 +32687,27 @@
       </c>
       <c r="O355" s="3" t="inlineStr">
         <is>
-          <t>CA - SO SACRAMENTO</t>
-        </is>
-      </c>
-      <c r="P355" s="3" t="inlineStr"/>
-      <c r="Q355" s="3" t="inlineStr"/>
+          <t>CA - FRESNO</t>
+        </is>
+      </c>
+      <c r="P355" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q355" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R355" s="3" t="inlineStr">
         <is>
-          <t>4T3LWRFV8RU******</t>
+          <t>2T3W1RFV9RW******</t>
         </is>
       </c>
       <c r="S355" s="3" t="inlineStr">
         <is>
-          <t>2.5L  4</t>
+          <t>2.5L 4</t>
         </is>
       </c>
       <c r="T355" s="3" t="inlineStr">
@@ -32709,19 +32717,19 @@
       </c>
       <c r="U355" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98336845/2024-toyota-rav4-le-ca-so-sacramento</t>
+          <t>https://www.copart.com/lot/98285395/salvage-2024-toyota-rav4-xle-ca-fresno</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>98433755</t>
+          <t>98336845</t>
         </is>
       </c>
       <c r="B356" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE</t>
+          <t>2024 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C356" s="6" t="n">
@@ -32739,14 +32747,10 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G356" s="6" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
-        </is>
-      </c>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="G356" s="6" t="inlineStr"/>
       <c r="H356" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -32757,10 +32761,16 @@
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J356" s="6" t="inlineStr"/>
-      <c r="K356" s="7" t="inlineStr"/>
+      <c r="J356" s="6" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
+      <c r="K356" s="7" t="n">
+        <v>23714</v>
+      </c>
       <c r="L356" s="7" t="n">
-        <v>30650</v>
+        <v>31247</v>
       </c>
       <c r="M356" s="7" t="n">
         <v>0</v>
@@ -32772,22 +32782,14 @@
       </c>
       <c r="O356" s="6" t="inlineStr">
         <is>
-          <t>IN - DYER</t>
-        </is>
-      </c>
-      <c r="P356" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-06 17:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q356" s="6" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>CA - SO SACRAMENTO</t>
+        </is>
+      </c>
+      <c r="P356" s="6" t="inlineStr"/>
+      <c r="Q356" s="6" t="inlineStr"/>
       <c r="R356" s="6" t="inlineStr">
         <is>
-          <t>2T3P1RFVXRC******</t>
+          <t>4T3LWRFV8RU******</t>
         </is>
       </c>
       <c r="S356" s="6" t="inlineStr">
@@ -32802,23 +32804,23 @@
       </c>
       <c r="U356" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98433755/salvage-2024-toyota-rav4-xle-in-dyer</t>
+          <t>https://www.copart.com/lot/98336845/2024-toyota-rav4-le-ca-so-sacramento</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>98542125</t>
+          <t>98433755</t>
         </is>
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2024 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
@@ -32832,7 +32834,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -32842,7 +32844,7 @@
       </c>
       <c r="H357" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I357" s="3" t="inlineStr">
@@ -32850,16 +32852,10 @@
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J357" s="3" t="inlineStr">
-        <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="K357" s="5" t="n">
-        <v>21333</v>
-      </c>
+      <c r="J357" s="3" t="inlineStr"/>
+      <c r="K357" s="5" t="inlineStr"/>
       <c r="L357" s="5" t="n">
-        <v>-1</v>
+        <v>30650</v>
       </c>
       <c r="M357" s="5" t="n">
         <v>0</v>
@@ -32871,14 +32867,22 @@
       </c>
       <c r="O357" s="3" t="inlineStr">
         <is>
-          <t>NC - CONCORD</t>
-        </is>
-      </c>
-      <c r="P357" s="3" t="inlineStr"/>
-      <c r="Q357" s="3" t="inlineStr"/>
+          <t>IN - DYER</t>
+        </is>
+      </c>
+      <c r="P357" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q357" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R357" s="3" t="inlineStr">
         <is>
-          <t>2T3C1RFV6NC******</t>
+          <t>2T3P1RFVXRC******</t>
         </is>
       </c>
       <c r="S357" s="3" t="inlineStr">
@@ -32893,23 +32897,23 @@
       </c>
       <c r="U357" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98542125/2022-toyota-rav4-xle-premium-nc-concord</t>
+          <t>https://www.copart.com/lot/98433755/salvage-2024-toyota-rav4-xle-in-dyer</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>98621805</t>
+          <t>98542125</t>
         </is>
       </c>
       <c r="B358" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 LE</t>
+          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C358" s="6" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D358" s="6" t="inlineStr">
         <is>
@@ -32923,34 +32927,34 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G358" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G358" s="6" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H358" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I358" s="6" t="inlineStr">
         <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J358" s="6" t="inlineStr">
+        <is>
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J358" s="6" t="inlineStr">
-        <is>
-          <t>SIDE</t>
-        </is>
-      </c>
       <c r="K358" s="7" t="n">
-        <v>7098</v>
+        <v>21333</v>
       </c>
       <c r="L358" s="7" t="n">
-        <v>31022</v>
+        <v>-1</v>
       </c>
       <c r="M358" s="7" t="n">
         <v>0</v>
@@ -32962,14 +32966,14 @@
       </c>
       <c r="O358" s="6" t="inlineStr">
         <is>
-          <t>TN - NASHVILLE</t>
+          <t>NC - CONCORD</t>
         </is>
       </c>
       <c r="P358" s="6" t="inlineStr"/>
       <c r="Q358" s="6" t="inlineStr"/>
       <c r="R358" s="6" t="inlineStr">
         <is>
-          <t>2T3F1RFVXRW******</t>
+          <t>2T3C1RFV6NC******</t>
         </is>
       </c>
       <c r="S358" s="6" t="inlineStr">
@@ -32984,23 +32988,23 @@
       </c>
       <c r="U358" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98621805/2024-toyota-rav4-le-tn-nashville</t>
+          <t>https://www.copart.com/lot/98542125/2022-toyota-rav4-xle-premium-nc-concord</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>98678215</t>
+          <t>98621805</t>
         </is>
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>2023 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
@@ -33029,15 +33033,19 @@
       </c>
       <c r="I359" s="3" t="inlineStr">
         <is>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J359" s="3" t="inlineStr">
+        <is>
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J359" s="3" t="inlineStr"/>
       <c r="K359" s="5" t="n">
-        <v>21857</v>
+        <v>7098</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>28236</v>
+        <v>31022</v>
       </c>
       <c r="M359" s="5" t="n">
         <v>0</v>
@@ -33049,22 +33057,14 @@
       </c>
       <c r="O359" s="3" t="inlineStr">
         <is>
-          <t>MA - FREETOWN</t>
-        </is>
-      </c>
-      <c r="P359" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-25 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q359" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>TN - NASHVILLE</t>
+        </is>
+      </c>
+      <c r="P359" s="3" t="inlineStr"/>
+      <c r="Q359" s="3" t="inlineStr"/>
       <c r="R359" s="3" t="inlineStr">
         <is>
-          <t>2T3F1RFV5PC******</t>
+          <t>2T3F1RFVXRW******</t>
         </is>
       </c>
       <c r="S359" s="3" t="inlineStr">
@@ -33079,23 +33079,23 @@
       </c>
       <c r="U359" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98678215/salvage-2023-toyota-rav4-le-ma-freetown</t>
+          <t>https://www.copart.com/lot/98621805/2024-toyota-rav4-le-tn-nashville</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>98937535</t>
+          <t>98678215</t>
         </is>
       </c>
       <c r="B360" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LIMITED</t>
+          <t>2023 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C360" s="6" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D360" s="6" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>LIMITED</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -33124,15 +33124,15 @@
       </c>
       <c r="I360" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>SIDE</t>
         </is>
       </c>
       <c r="J360" s="6" t="inlineStr"/>
       <c r="K360" s="7" t="n">
-        <v>2393</v>
+        <v>21857</v>
       </c>
       <c r="L360" s="7" t="n">
-        <v>38492</v>
+        <v>28236</v>
       </c>
       <c r="M360" s="7" t="n">
         <v>0</v>
@@ -33144,14 +33144,22 @@
       </c>
       <c r="O360" s="6" t="inlineStr">
         <is>
-          <t>MN - MINNEAPOLIS NORTH</t>
-        </is>
-      </c>
-      <c r="P360" s="6" t="inlineStr"/>
-      <c r="Q360" s="6" t="inlineStr"/>
+          <t>MA - FREETOWN</t>
+        </is>
+      </c>
+      <c r="P360" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-25 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q360" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R360" s="6" t="inlineStr">
         <is>
-          <t>2T3N1RFV2SW******</t>
+          <t>2T3F1RFV5PC******</t>
         </is>
       </c>
       <c r="S360" s="6" t="inlineStr">
@@ -33166,19 +33174,19 @@
       </c>
       <c r="U360" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/98937535/2025-toyota-rav4-limited-mn-minneapolis-north</t>
+          <t>https://www.copart.com/lot/98678215/salvage-2023-toyota-rav4-le-ma-freetown</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>99205765</t>
+          <t>98937535</t>
         </is>
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4</t>
+          <t>2025 TOYOTA RAV4 LIMITED</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -33194,10 +33202,14 @@
           <t>RAV4</t>
         </is>
       </c>
-      <c r="F361" s="3" t="inlineStr"/>
-      <c r="G361" s="3" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+      <c r="F361" s="3" t="inlineStr">
+        <is>
+          <t>LIMITED</t>
+        </is>
+      </c>
+      <c r="G361" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H361" s="3" t="inlineStr">
@@ -33210,16 +33222,12 @@
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J361" s="3" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+      <c r="J361" s="3" t="inlineStr"/>
       <c r="K361" s="5" t="n">
-        <v>10449</v>
+        <v>2393</v>
       </c>
       <c r="L361" s="5" t="n">
-        <v>33160</v>
+        <v>38492</v>
       </c>
       <c r="M361" s="5" t="n">
         <v>0</v>
@@ -33231,14 +33239,14 @@
       </c>
       <c r="O361" s="3" t="inlineStr">
         <is>
-          <t>NC - RALEIGH</t>
+          <t>MN - MINNEAPOLIS NORTH</t>
         </is>
       </c>
       <c r="P361" s="3" t="inlineStr"/>
       <c r="Q361" s="3" t="inlineStr"/>
       <c r="R361" s="3" t="inlineStr">
         <is>
-          <t>JTMMWRFV0SD******</t>
+          <t>2T3N1RFV2SW******</t>
         </is>
       </c>
       <c r="S361" s="3" t="inlineStr">
@@ -33253,23 +33261,23 @@
       </c>
       <c r="U361" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99205765/2025-toyota-rav4-nc-raleigh</t>
+          <t>https://www.copart.com/lot/98937535/2025-toyota-rav4-limited-mn-minneapolis-north</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>99216065</t>
+          <t>99205765</t>
         </is>
       </c>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 LE</t>
+          <t>2025 TOYOTA RAV4</t>
         </is>
       </c>
       <c r="C362" s="6" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D362" s="6" t="inlineStr">
         <is>
@@ -33281,11 +33289,7 @@
           <t>RAV4</t>
         </is>
       </c>
-      <c r="F362" s="6" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="F362" s="6" t="inlineStr"/>
       <c r="G362" s="6" t="inlineStr">
         <is>
           <t>ENHANCED VEHICLES</t>
@@ -33293,18 +33297,24 @@
       </c>
       <c r="H362" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I362" s="6" t="inlineStr">
         <is>
-          <t>MINOR DENT/SCRATCHES</t>
-        </is>
-      </c>
-      <c r="J362" s="6" t="inlineStr"/>
-      <c r="K362" s="7" t="inlineStr"/>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J362" s="6" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
+      <c r="K362" s="7" t="n">
+        <v>10449</v>
+      </c>
       <c r="L362" s="7" t="n">
-        <v>23908</v>
+        <v>33160</v>
       </c>
       <c r="M362" s="7" t="n">
         <v>0</v>
@@ -33316,18 +33326,14 @@
       </c>
       <c r="O362" s="6" t="inlineStr">
         <is>
-          <t>IL - CHICAGO NORTH</t>
+          <t>NC - RALEIGH</t>
         </is>
       </c>
       <c r="P362" s="6" t="inlineStr"/>
-      <c r="Q362" s="6" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+      <c r="Q362" s="6" t="inlineStr"/>
       <c r="R362" s="6" t="inlineStr">
         <is>
-          <t>2T3G1RFV7NW******</t>
+          <t>JTMMWRFV0SD******</t>
         </is>
       </c>
       <c r="S362" s="6" t="inlineStr">
@@ -33342,23 +33348,23 @@
       </c>
       <c r="U362" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99216065/salvage-2022-toyota-rav4-le-il-chicago-north</t>
+          <t>https://www.copart.com/lot/99205765/2025-toyota-rav4-nc-raleigh</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>99251225</t>
+          <t>99216065</t>
         </is>
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 WOODLAND EDITION</t>
+          <t>2022 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C363" s="3" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
@@ -33372,7 +33378,7 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>WOODLAND EDITION</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -33382,43 +33388,33 @@
       </c>
       <c r="H363" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I363" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J363" s="3" t="inlineStr">
-        <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="K363" s="5" t="n">
-        <v>12582</v>
-      </c>
+          <t>MINOR DENT/SCRATCHES</t>
+        </is>
+      </c>
+      <c r="J363" s="3" t="inlineStr"/>
+      <c r="K363" s="5" t="inlineStr"/>
       <c r="L363" s="5" t="n">
-        <v>35294</v>
+        <v>23908</v>
       </c>
       <c r="M363" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N363" s="3" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O363" s="3" t="inlineStr">
         <is>
-          <t>CO - DENVER</t>
-        </is>
-      </c>
-      <c r="P363" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-24 18:00 UTC</t>
-        </is>
-      </c>
+          <t>IL - CHICAGO NORTH</t>
+        </is>
+      </c>
+      <c r="P363" s="3" t="inlineStr"/>
       <c r="Q363" s="3" t="inlineStr">
         <is>
           <t>SALVAGE TITLE</t>
@@ -33426,7 +33422,7 @@
       </c>
       <c r="R363" s="3" t="inlineStr">
         <is>
-          <t>2T3UWRFV3RW******</t>
+          <t>2T3G1RFV7NW******</t>
         </is>
       </c>
       <c r="S363" s="3" t="inlineStr">
@@ -33441,19 +33437,19 @@
       </c>
       <c r="U363" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99251225/salvage-2024-toyota-rav4-woodland-edition-co-denver</t>
+          <t>https://www.copart.com/lot/99216065/salvage-2022-toyota-rav4-le-il-chicago-north</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>99282985</t>
+          <t>99251225</t>
         </is>
       </c>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2024 TOYOTA RAV4 WOODLAND EDITION</t>
         </is>
       </c>
       <c r="C364" s="6" t="n">
@@ -33471,12 +33467,12 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
-        </is>
-      </c>
-      <c r="G364" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>WOODLAND EDITION</t>
+        </is>
+      </c>
+      <c r="G364" s="6" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H364" s="6" t="inlineStr">
@@ -33486,38 +33482,46 @@
       </c>
       <c r="I364" s="6" t="inlineStr">
         <is>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J364" s="6" t="inlineStr">
+        <is>
           <t>SIDE</t>
         </is>
       </c>
-      <c r="J364" s="6" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
       <c r="K364" s="7" t="n">
-        <v>12493</v>
+        <v>12582</v>
       </c>
       <c r="L364" s="7" t="n">
-        <v>33959</v>
+        <v>35294</v>
       </c>
       <c r="M364" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N364" s="6" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O364" s="6" t="inlineStr">
         <is>
-          <t>HI - HONOLULU</t>
-        </is>
-      </c>
-      <c r="P364" s="6" t="inlineStr"/>
-      <c r="Q364" s="6" t="inlineStr"/>
+          <t>CO - DENVER</t>
+        </is>
+      </c>
+      <c r="P364" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-24 18:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q364" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R364" s="6" t="inlineStr">
         <is>
-          <t>JTMC1RFV8RD******</t>
+          <t>2T3UWRFV3RW******</t>
         </is>
       </c>
       <c r="S364" s="6" t="inlineStr">
@@ -33532,23 +33536,23 @@
       </c>
       <c r="U364" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99282985/2024-toyota-rav4-xle-premium-hi-honolulu</t>
+          <t>https://www.copart.com/lot/99251225/salvage-2024-toyota-rav4-woodland-edition-co-denver</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>99392955</t>
+          <t>99282985</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C365" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
@@ -33562,12 +33566,12 @@
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="G365" s="3" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G365" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H365" s="3" t="inlineStr">
@@ -33577,15 +33581,19 @@
       </c>
       <c r="I365" s="3" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J365" s="3" t="inlineStr"/>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J365" s="3" t="inlineStr">
+        <is>
+          <t>FRONT END</t>
+        </is>
+      </c>
       <c r="K365" s="5" t="n">
-        <v>11244</v>
+        <v>12493</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>31881</v>
+        <v>33959</v>
       </c>
       <c r="M365" s="5" t="n">
         <v>0</v>
@@ -33597,22 +33605,14 @@
       </c>
       <c r="O365" s="3" t="inlineStr">
         <is>
-          <t>CA - SUN VALLEY</t>
-        </is>
-      </c>
-      <c r="P365" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q365" s="3" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>HI - HONOLULU</t>
+        </is>
+      </c>
+      <c r="P365" s="3" t="inlineStr"/>
+      <c r="Q365" s="3" t="inlineStr"/>
       <c r="R365" s="3" t="inlineStr">
         <is>
-          <t>JTMMWRFV6SD******</t>
+          <t>JTMC1RFV8RD******</t>
         </is>
       </c>
       <c r="S365" s="3" t="inlineStr">
@@ -33627,23 +33627,23 @@
       </c>
       <c r="U365" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99392955/salvage-2025-toyota-rav4-le-ca-sun-valley</t>
+          <t>https://www.copart.com/lot/99282985/2024-toyota-rav4-xle-premium-hi-honolulu</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>99469625</t>
+          <t>99392955</t>
         </is>
       </c>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
+          <t>2025 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C366" s="6" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D366" s="6" t="inlineStr">
         <is>
@@ -33657,12 +33657,12 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>XLE PREMIUM</t>
-        </is>
-      </c>
-      <c r="G366" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="G366" s="6" t="inlineStr">
+        <is>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H366" s="6" t="inlineStr">
@@ -33677,27 +33677,27 @@
       </c>
       <c r="J366" s="6" t="inlineStr"/>
       <c r="K366" s="7" t="n">
-        <v>23566</v>
+        <v>11244</v>
       </c>
       <c r="L366" s="7" t="n">
-        <v>30084</v>
+        <v>31881</v>
       </c>
       <c r="M366" s="7" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="N366" s="6" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O366" s="6" t="inlineStr">
         <is>
-          <t>TX - DALLAS</t>
+          <t>CA - SUN VALLEY</t>
         </is>
       </c>
       <c r="P366" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12 17:00 UTC</t>
+          <t>2026-03-16 19:00 UTC</t>
         </is>
       </c>
       <c r="Q366" s="6" t="inlineStr">
@@ -33707,7 +33707,7 @@
       </c>
       <c r="R366" s="6" t="inlineStr">
         <is>
-          <t>2T3C1RFV5NW******</t>
+          <t>JTMMWRFV6SD******</t>
         </is>
       </c>
       <c r="S366" s="6" t="inlineStr">
@@ -33722,23 +33722,23 @@
       </c>
       <c r="U366" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99469625/salvage-2022-toyota-rav4-xle-premium-tx-dallas</t>
+          <t>https://www.copart.com/lot/99392955/salvage-2025-toyota-rav4-le-ca-sun-valley</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>99642525</t>
+          <t>99469625</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
@@ -33752,12 +33752,12 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G367" s="3" t="inlineStr">
-        <is>
-          <t>ENHANCED VEHICLES</t>
+          <t>XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="G367" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H367" s="3" t="inlineStr">
@@ -33767,38 +33767,42 @@
       </c>
       <c r="I367" s="3" t="inlineStr">
         <is>
-          <t>SIDE</t>
-        </is>
-      </c>
-      <c r="J367" s="3" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J367" s="3" t="inlineStr"/>
       <c r="K367" s="5" t="n">
-        <v>14551</v>
+        <v>23566</v>
       </c>
       <c r="L367" s="5" t="n">
-        <v>30815</v>
+        <v>30084</v>
       </c>
       <c r="M367" s="5" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="N367" s="3" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O367" s="3" t="inlineStr">
         <is>
-          <t>VA - RICHMOND</t>
-        </is>
-      </c>
-      <c r="P367" s="3" t="inlineStr"/>
-      <c r="Q367" s="3" t="inlineStr"/>
+          <t>TX - DALLAS</t>
+        </is>
+      </c>
+      <c r="P367" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q367" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R367" s="3" t="inlineStr">
         <is>
-          <t>JTMRWRFV1SJ******</t>
+          <t>2T3C1RFV5NW******</t>
         </is>
       </c>
       <c r="S367" s="3" t="inlineStr">
@@ -33813,14 +33817,14 @@
       </c>
       <c r="U367" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99642525/2025-toyota-rav4-xle-va-richmond</t>
+          <t>https://www.copart.com/lot/99469625/salvage-2022-toyota-rav4-xle-premium-tx-dallas</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>99770855</t>
+          <t>99642525</t>
         </is>
       </c>
       <c r="B368" s="6" t="inlineStr">
@@ -33848,7 +33852,7 @@
       </c>
       <c r="G368" s="6" t="inlineStr">
         <is>
-          <t>ENGINE START PROGRAM</t>
+          <t>ENHANCED VEHICLES</t>
         </is>
       </c>
       <c r="H368" s="6" t="inlineStr">
@@ -33863,17 +33867,17 @@
       </c>
       <c r="J368" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>FRONT END</t>
         </is>
       </c>
       <c r="K368" s="7" t="n">
-        <v>9078</v>
+        <v>14551</v>
       </c>
       <c r="L368" s="7" t="n">
-        <v>28342</v>
+        <v>30815</v>
       </c>
       <c r="M368" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N368" s="6" t="inlineStr">
         <is>
@@ -33882,27 +33886,19 @@
       </c>
       <c r="O368" s="6" t="inlineStr">
         <is>
-          <t>FL - JACKSONVILLE NORTH</t>
-        </is>
-      </c>
-      <c r="P368" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-11 14:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q368" s="6" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>VA - RICHMOND</t>
+        </is>
+      </c>
+      <c r="P368" s="6" t="inlineStr"/>
+      <c r="Q368" s="6" t="inlineStr"/>
       <c r="R368" s="6" t="inlineStr">
         <is>
-          <t>2T3W1RFV2SC******</t>
+          <t>JTMRWRFV1SJ******</t>
         </is>
       </c>
       <c r="S368" s="6" t="inlineStr">
         <is>
-          <t>2.5L 4</t>
+          <t>2.5L  4</t>
         </is>
       </c>
       <c r="T368" s="6" t="inlineStr">
@@ -33912,19 +33908,19 @@
       </c>
       <c r="U368" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99770855/salvage-2025-toyota-rav4-xle-fl-jacksonville-north</t>
+          <t>https://www.copart.com/lot/99642525/2025-toyota-rav4-xle-va-richmond</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>99780885</t>
+          <t>99770855</t>
         </is>
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LIMITED</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C369" s="3" t="n">
@@ -33942,7 +33938,7 @@
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
-          <t>LIMITED</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
@@ -33962,31 +33958,31 @@
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
-          <t>UNDERCARRIAGE</t>
+          <t>REAR END</t>
         </is>
       </c>
       <c r="K369" s="5" t="n">
-        <v>8183</v>
+        <v>9078</v>
       </c>
       <c r="L369" s="5" t="n">
-        <v>-1</v>
+        <v>28342</v>
       </c>
       <c r="M369" s="5" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="N369" s="3" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O369" s="3" t="inlineStr">
         <is>
-          <t>IA - DES MOINES</t>
+          <t>FL - JACKSONVILLE NORTH</t>
         </is>
       </c>
       <c r="P369" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10 17:00 UTC</t>
+          <t>2026-03-11 14:00 UTC</t>
         </is>
       </c>
       <c r="Q369" s="3" t="inlineStr">
@@ -33996,12 +33992,12 @@
       </c>
       <c r="R369" s="3" t="inlineStr">
         <is>
-          <t>4T3D6RFV0SU******</t>
+          <t>2T3W1RFV2SC******</t>
         </is>
       </c>
       <c r="S369" s="3" t="inlineStr">
         <is>
-          <t>2.5L  4</t>
+          <t>2.5L 4</t>
         </is>
       </c>
       <c r="T369" s="3" t="inlineStr">
@@ -34011,19 +34007,19 @@
       </c>
       <c r="U369" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99780885/salvage-2025-toyota-rav4-limited-ia-des-moines</t>
+          <t>https://www.copart.com/lot/99770855/salvage-2025-toyota-rav4-xle-fl-jacksonville-north</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>99781835</t>
+          <t>99780885</t>
         </is>
       </c>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 LIMITED</t>
         </is>
       </c>
       <c r="C370" s="6" t="n">
@@ -34041,12 +34037,12 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G370" s="4" t="inlineStr">
-        <is>
-          <t>RUNS AND DRIVES</t>
+          <t>LIMITED</t>
+        </is>
+      </c>
+      <c r="G370" s="6" t="inlineStr">
+        <is>
+          <t>ENGINE START PROGRAM</t>
         </is>
       </c>
       <c r="H370" s="6" t="inlineStr">
@@ -34056,34 +34052,46 @@
       </c>
       <c r="I370" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
-        </is>
-      </c>
-      <c r="J370" s="6" t="inlineStr"/>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J370" s="6" t="inlineStr">
+        <is>
+          <t>UNDERCARRIAGE</t>
+        </is>
+      </c>
       <c r="K370" s="7" t="n">
-        <v>11137</v>
+        <v>8183</v>
       </c>
       <c r="L370" s="7" t="n">
-        <v>28475</v>
+        <v>-1</v>
       </c>
       <c r="M370" s="7" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="N370" s="6" t="inlineStr">
         <is>
-          <t>🔑 Broker</t>
+          <t>✅ NLR</t>
         </is>
       </c>
       <c r="O370" s="6" t="inlineStr">
         <is>
-          <t>GA - CARTERSVILLE</t>
-        </is>
-      </c>
-      <c r="P370" s="6" t="inlineStr"/>
-      <c r="Q370" s="6" t="inlineStr"/>
+          <t>IA - DES MOINES</t>
+        </is>
+      </c>
+      <c r="P370" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q370" s="6" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
       <c r="R370" s="6" t="inlineStr">
         <is>
-          <t>2T3W1RFV2SC******</t>
+          <t>4T3D6RFV0SU******</t>
         </is>
       </c>
       <c r="S370" s="6" t="inlineStr">
@@ -34098,23 +34106,23 @@
       </c>
       <c r="U370" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99781835/2025-toyota-rav4-xle-ga-cartersville</t>
+          <t>https://www.copart.com/lot/99780885/salvage-2025-toyota-rav4-limited-ia-des-moines</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>99813365</t>
+          <t>99781835</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>2024 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
@@ -34143,19 +34151,15 @@
       </c>
       <c r="I371" s="3" t="inlineStr">
         <is>
-          <t>VANDALISM</t>
-        </is>
-      </c>
-      <c r="J371" s="3" t="inlineStr">
-        <is>
-          <t>FRONT END</t>
-        </is>
-      </c>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J371" s="3" t="inlineStr"/>
       <c r="K371" s="5" t="n">
-        <v>28237</v>
+        <v>11137</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>-1</v>
+        <v>28475</v>
       </c>
       <c r="M371" s="5" t="n">
         <v>0</v>
@@ -34167,14 +34171,14 @@
       </c>
       <c r="O371" s="3" t="inlineStr">
         <is>
-          <t>QC - MONTREAL</t>
+          <t>GA - CARTERSVILLE</t>
         </is>
       </c>
       <c r="P371" s="3" t="inlineStr"/>
       <c r="Q371" s="3" t="inlineStr"/>
       <c r="R371" s="3" t="inlineStr">
         <is>
-          <t>2T3R1RFV5RW******</t>
+          <t>2T3W1RFV2SC******</t>
         </is>
       </c>
       <c r="S371" s="3" t="inlineStr">
@@ -34189,23 +34193,23 @@
       </c>
       <c r="U371" s="3" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99813365/2024-toyota-rav4-xle-qc-montreal</t>
+          <t>https://www.copart.com/lot/99781835/2025-toyota-rav4-xle-ga-cartersville</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>99835885</t>
+          <t>99813365</t>
         </is>
       </c>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>2025 TOYOTA RAV4 LE</t>
+          <t>2024 TOYOTA RAV4 XLE</t>
         </is>
       </c>
       <c r="C372" s="6" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D372" s="6" t="inlineStr">
         <is>
@@ -34219,7 +34223,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="G372" s="4" t="inlineStr">
@@ -34234,46 +34238,38 @@
       </c>
       <c r="I372" s="6" t="inlineStr">
         <is>
-          <t>SIDE</t>
+          <t>VANDALISM</t>
         </is>
       </c>
       <c r="J372" s="6" t="inlineStr">
         <is>
-          <t>REAR END</t>
+          <t>FRONT END</t>
         </is>
       </c>
       <c r="K372" s="7" t="n">
-        <v>4342</v>
+        <v>28237</v>
       </c>
       <c r="L372" s="7" t="n">
-        <v>29066</v>
+        <v>-1</v>
       </c>
       <c r="M372" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N372" s="6" t="inlineStr">
         <is>
-          <t>✅ NLR</t>
+          <t>🔑 Broker</t>
         </is>
       </c>
       <c r="O372" s="6" t="inlineStr">
         <is>
-          <t>MS - JACKSON</t>
-        </is>
-      </c>
-      <c r="P372" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-13 17:00 UTC</t>
-        </is>
-      </c>
-      <c r="Q372" s="6" t="inlineStr">
-        <is>
-          <t>SALVAGE TITLE</t>
-        </is>
-      </c>
+          <t>QC - MONTREAL</t>
+        </is>
+      </c>
+      <c r="P372" s="6" t="inlineStr"/>
+      <c r="Q372" s="6" t="inlineStr"/>
       <c r="R372" s="6" t="inlineStr">
         <is>
-          <t>2T3H1RFVXSC******</t>
+          <t>2T3R1RFV5RW******</t>
         </is>
       </c>
       <c r="S372" s="6" t="inlineStr">
@@ -34288,23 +34284,23 @@
       </c>
       <c r="U372" s="6" t="inlineStr">
         <is>
-          <t>https://www.copart.com/lot/99835885/salvage-2025-toyota-rav4-le-ms-jackson</t>
+          <t>https://www.copart.com/lot/99813365/2024-toyota-rav4-xle-qc-montreal</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>99850375</t>
+          <t>99835885</t>
         </is>
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>2023 TOYOTA RAV4 XLE</t>
+          <t>2025 TOYOTA RAV4 LE</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
@@ -34318,12 +34314,12 @@
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="G373" s="3" t="inlineStr">
-        <is>
-          <t>ENGINE START PROGRAM</t>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="G373" s="4" t="inlineStr">
+        <is>
+          <t>RUNS AND DRIVES</t>
         </is>
       </c>
       <c r="H373" s="3" t="inlineStr">
@@ -34333,76 +34329,175 @@
       </c>
       <c r="I373" s="3" t="inlineStr">
         <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="J373" s="3" t="inlineStr">
+        <is>
           <t>REAR END</t>
         </is>
       </c>
-      <c r="J373" s="3" t="inlineStr"/>
       <c r="K373" s="5" t="n">
-        <v>25382</v>
+        <v>4342</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>29177</v>
+        <v>29066</v>
       </c>
       <c r="M373" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N373" s="3" t="inlineStr">
         <is>
+          <t>✅ NLR</t>
+        </is>
+      </c>
+      <c r="O373" s="3" t="inlineStr">
+        <is>
+          <t>MS - JACKSON</t>
+        </is>
+      </c>
+      <c r="P373" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-13 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="Q373" s="3" t="inlineStr">
+        <is>
+          <t>SALVAGE TITLE</t>
+        </is>
+      </c>
+      <c r="R373" s="3" t="inlineStr">
+        <is>
+          <t>2T3H1RFVXSC******</t>
+        </is>
+      </c>
+      <c r="S373" s="3" t="inlineStr">
+        <is>
+          <t>2.5L  4</t>
+        </is>
+      </c>
+      <c r="T373" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:39:57 UTC</t>
+        </is>
+      </c>
+      <c r="U373" s="3" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/99835885/salvage-2025-toyota-rav4-le-ms-jackson</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="6" t="inlineStr">
+        <is>
+          <t>99850375</t>
+        </is>
+      </c>
+      <c r="B374" s="6" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C374" s="6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D374" s="6" t="inlineStr">
+        <is>
+          <t>TOYOTA</t>
+        </is>
+      </c>
+      <c r="E374" s="6" t="inlineStr">
+        <is>
+          <t>RAV4</t>
+        </is>
+      </c>
+      <c r="F374" s="6" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="G374" s="6" t="inlineStr">
+        <is>
+          <t>ENGINE START PROGRAM</t>
+        </is>
+      </c>
+      <c r="H374" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I374" s="6" t="inlineStr">
+        <is>
+          <t>REAR END</t>
+        </is>
+      </c>
+      <c r="J374" s="6" t="inlineStr"/>
+      <c r="K374" s="7" t="n">
+        <v>25382</v>
+      </c>
+      <c r="L374" s="7" t="n">
+        <v>29177</v>
+      </c>
+      <c r="M374" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N374" s="6" t="inlineStr">
+        <is>
           <t>🔑 Broker</t>
         </is>
       </c>
-      <c r="O373" s="3" t="inlineStr">
+      <c r="O374" s="6" t="inlineStr">
         <is>
           <t>MA - NORTH BOSTON</t>
         </is>
       </c>
-      <c r="P373" s="3" t="inlineStr"/>
-      <c r="Q373" s="3" t="inlineStr"/>
-      <c r="R373" s="3" t="inlineStr">
+      <c r="P374" s="6" t="inlineStr"/>
+      <c r="Q374" s="6" t="inlineStr"/>
+      <c r="R374" s="6" t="inlineStr">
         <is>
           <t>2T3P1RFVXPW******</t>
         </is>
       </c>
-      <c r="S373" s="3" t="inlineStr">
+      <c r="S374" s="6" t="inlineStr">
         <is>
           <t>2.5L  4</t>
         </is>
       </c>
-      <c r="T373" s="3" t="inlineStr">
+      <c r="T374" s="6" t="inlineStr">
         <is>
           <t>2026-03-11 12:39:57 UTC</t>
         </is>
       </c>
-      <c r="U373" s="3" t="inlineStr">
+      <c r="U374" s="6" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/99850375/2023-toyota-rav4-xle-ma-north-boston</t>
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" s="8" t="inlineStr">
+    <row r="375">
+      <c r="A375" s="8" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B374" s="9" t="inlineStr">
-        <is>
-          <t>Total Lots: 371</t>
-        </is>
-      </c>
-      <c r="C374" s="10" t="inlineStr">
+      <c r="B375" s="9" t="inlineStr">
+        <is>
+          <t>Total Lots: 372</t>
+        </is>
+      </c>
+      <c r="C375" s="10" t="inlineStr">
         <is>
           <t>NLR: 35</t>
         </is>
       </c>
-      <c r="D374" s="9" t="inlineStr">
-        <is>
-          <t>Broker: 336</t>
-        </is>
-      </c>
-      <c r="E374" s="10" t="inlineStr">
-        <is>
-          <t>Runs &amp; Drives: 237</t>
+      <c r="D375" s="9" t="inlineStr">
+        <is>
+          <t>Broker: 337</t>
+        </is>
+      </c>
+      <c r="E375" s="10" t="inlineStr">
+        <is>
+          <t>Runs &amp; Drives: 238</t>
         </is>
       </c>
     </row>
